--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46224.9867977199</v>
+        <v>46226.173131180556</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>44</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46227.73713165509</v>
+        <v>46230.74156164352</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>44</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="343">
   <si>
     <t>50001577- "XEMORTIZ LA CANTERA"</t>
   </si>
@@ -397,28 +397,34 @@
     <t xml:space="preserve">Plano Preliminar OT 4376 </t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria y diseñoo:,Plano Definitivos OT 4376 </t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1216771806162105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Definitivos OT 4376 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria y diseñoo:,Check Planos OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771806169487</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria y diseñoo:,Plano Definitivos OT 4376 </t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1216771806162105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Definitivos OT 4376 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria y diseñoo:,Check Planos OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771806169487</t>
   </si>
   <si>
     <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Propuesta Fabricación externa  OT 4376 ,Propuesta Mecanizado OT 4376 ,Propuesta Corte plasma  OT 4376 ,propuesta Corte laser OT 4376 ,Ingenieria y diseñoo:,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
@@ -3496,7 +3502,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46227.18049490741</v>
+        <v>46231.54222418982</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>127</v>
@@ -3559,7 +3565,7 @@
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46224.987844421295</v>
+        <v>46231.54226138889</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>133</v>
@@ -3631,10 +3637,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3658,7 +3664,7 @@
         <v>133</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3678,7 +3684,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B39" s="8">
         <v>46224.89596851852</v>
@@ -3688,16 +3694,16 @@
         <v>46224.9887275463</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I39" s="8">
         <v>46290</v>
@@ -3718,7 +3724,7 @@
         <v>124</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>124</v>
@@ -3741,7 +3747,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46224.89597322917</v>
@@ -3751,16 +3757,16 @@
         <v>46224.98802077546</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3776,13 +3782,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3792,7 +3798,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8">
         <v>46224.89597747685</v>
@@ -3802,16 +3808,16 @@
         <v>46224.988017592594</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="8">
@@ -3827,13 +3833,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3843,7 +3849,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46224.89600425926</v>
@@ -3853,16 +3859,16 @@
         <v>46224.98801423611</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -3878,13 +3884,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3894,7 +3900,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B43" s="8">
         <v>46224.90846989583</v>
@@ -3904,16 +3910,16 @@
         <v>46224.988011203706</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="8">
@@ -3929,13 +3935,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3945,7 +3951,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B44" s="5">
         <v>46224.908482824074</v>
@@ -3955,16 +3961,16 @@
         <v>46224.98800859954</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -3980,13 +3986,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -3996,7 +4002,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B45" s="8">
         <v>46224.908498171295</v>
@@ -4006,16 +4012,16 @@
         <v>46224.98800302083</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4031,13 +4037,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4047,7 +4053,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B46" s="5">
         <v>46224.89600854166</v>
@@ -4057,7 +4063,7 @@
         <v>46224.97705253473</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4081,7 +4087,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4094,7 +4100,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B47" s="8">
         <v>46224.896012384255</v>
@@ -4104,16 +4110,16 @@
         <v>46224.9888250463</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="8">
@@ -4129,13 +4135,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>89</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q47" s="8">
         <v>46260</v>
@@ -4155,7 +4161,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B48" s="5">
         <v>46224.896018368054</v>
@@ -4165,16 +4171,16 @@
         <v>46224.98882244213</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I48" s="5">
         <v>46260</v>
@@ -4192,13 +4198,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q48" s="5">
         <v>46260</v>
@@ -4218,7 +4224,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B49" s="8">
         <v>46224.89602424769</v>
@@ -4228,16 +4234,16 @@
         <v>46224.98881765046</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I49" s="8">
         <v>46260</v>
@@ -4255,13 +4261,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>105</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q49" s="8">
         <v>46260</v>
@@ -4281,7 +4287,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B50" s="5">
         <v>46224.89603097222</v>
@@ -4291,7 +4297,7 @@
         <v>46224.98890766204</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4318,13 +4324,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q50" s="5">
         <v>46261</v>
@@ -4344,7 +4350,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B51" s="8">
         <v>46224.89603738426</v>
@@ -4354,7 +4360,7 @@
         <v>46224.9889028125</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -4381,13 +4387,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q51" s="8">
         <v>46261</v>
@@ -4407,7 +4413,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B52" s="5">
         <v>46224.89604363426</v>
@@ -4417,7 +4423,7 @@
         <v>46224.988900625</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4444,13 +4450,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q52" s="5">
         <v>46261</v>
@@ -4470,7 +4476,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B53" s="8">
         <v>46224.89604989583</v>
@@ -4480,7 +4486,7 @@
         <v>46224.978400416665</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4504,7 +4510,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4517,7 +4523,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B54" s="5">
         <v>46224.8960534375</v>
@@ -4533,10 +4539,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I54" s="5">
         <v>46262</v>
@@ -4554,13 +4560,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>73</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q54" s="5">
         <v>46266</v>
@@ -4580,7 +4586,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B55" s="8">
         <v>46224.89605969907</v>
@@ -4596,10 +4602,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I55" s="8">
         <v>46267</v>
@@ -4617,13 +4623,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q55" s="8">
         <v>46273</v>
@@ -4643,7 +4649,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B56" s="5">
         <v>46224.89606466435</v>
@@ -4653,16 +4659,16 @@
         <v>46224.992601238424</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I56" s="5">
         <v>46267</v>
@@ -4683,10 +4689,10 @@
         <v>117</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4696,7 +4702,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B57" s="8">
         <v>46224.89607361111</v>
@@ -4706,16 +4712,16 @@
         <v>46224.992598055556</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I57" s="8">
         <v>46267</v>
@@ -4736,10 +4742,10 @@
         <v>117</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -4749,7 +4755,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B58" s="5">
         <v>46224.89613331019</v>
@@ -4759,16 +4765,16 @@
         <v>46224.99259486111</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I58" s="5">
         <v>46267</v>
@@ -4789,10 +4795,10 @@
         <v>117</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4802,7 +4808,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B59" s="8">
         <v>46224.90866162037</v>
@@ -4812,16 +4818,16 @@
         <v>46224.992584293985</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I59" s="8">
         <v>46267</v>
@@ -4845,7 +4851,7 @@
         <v>74</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -4855,7 +4861,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B60" s="5">
         <v>46224.90867304398</v>
@@ -4865,16 +4871,16 @@
         <v>46224.99258355324</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I60" s="5">
         <v>46267</v>
@@ -4898,7 +4904,7 @@
         <v>74</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4908,7 +4914,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B61" s="8">
         <v>46224.90868626157</v>
@@ -4918,16 +4924,16 @@
         <v>46224.99258276621</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I61" s="8">
         <v>46267</v>
@@ -4951,7 +4957,7 @@
         <v>74</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -4961,7 +4967,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B62" s="5">
         <v>46224.89614391203</v>
@@ -4971,7 +4977,7 @@
         <v>46225.00135394676</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -4998,13 +5004,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q62" s="5">
         <v>46274</v>
@@ -5024,7 +5030,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B63" s="8">
         <v>46224.896148935186</v>
@@ -5034,7 +5040,7 @@
         <v>46225.00151636574</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5061,13 +5067,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5077,7 +5083,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B64" s="5">
         <v>46224.89615454861</v>
@@ -5087,7 +5093,7 @@
         <v>46225.00151569444</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5114,13 +5120,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5130,7 +5136,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B65" s="8">
         <v>46224.89616001157</v>
@@ -5140,7 +5146,7 @@
         <v>46225.00151508102</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5167,13 +5173,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5183,7 +5189,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B66" s="5">
         <v>46224.90877734954</v>
@@ -5193,7 +5199,7 @@
         <v>46225.00151444445</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5220,13 +5226,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5236,7 +5242,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B67" s="8">
         <v>46224.90879113426</v>
@@ -5246,7 +5252,7 @@
         <v>46225.00151381944</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5273,13 +5279,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5289,7 +5295,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B68" s="5">
         <v>46224.90880622686</v>
@@ -5299,7 +5305,7 @@
         <v>46225.001513020834</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5326,13 +5332,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5342,7 +5348,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B69" s="8">
         <v>46224.89616483796</v>
@@ -5352,7 +5358,7 @@
         <v>46224.97892864583</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5376,7 +5382,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5389,26 +5395,26 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B70" s="5">
         <v>46224.89616836805</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46225.00166908564</v>
+        <v>46231.17180152777</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I70" s="5">
         <v>46230</v>
@@ -5426,13 +5432,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>52</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q70" s="5">
         <v>46231</v>
@@ -5452,26 +5458,26 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B71" s="8">
         <v>46224.89617388889</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46225.00166623843</v>
+        <v>46231.17181008102</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I71" s="8">
         <v>46230</v>
@@ -5489,13 +5495,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>58</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q71" s="8">
         <v>46231</v>
@@ -5515,26 +5521,26 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B72" s="5">
         <v>46224.89617931713</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46225.00166346064</v>
+        <v>46231.17181144676</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I72" s="5">
         <v>46230</v>
@@ -5552,13 +5558,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>61</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -5578,7 +5584,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B73" s="8">
         <v>46224.896184826386</v>
@@ -5588,7 +5594,7 @@
         <v>46224.981535706014</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5612,7 +5618,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5625,7 +5631,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B74" s="5">
         <v>46224.89618846065</v>
@@ -5635,7 +5641,7 @@
         <v>46225.00179069444</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5662,13 +5668,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q74" s="5">
         <v>46281</v>
@@ -5688,7 +5694,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B75" s="8">
         <v>46224.89619313658</v>
@@ -5698,7 +5704,7 @@
         <v>46225.00190993056</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5725,13 +5731,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -5741,7 +5747,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B76" s="5">
         <v>46224.89619747685</v>
@@ -5751,7 +5757,7 @@
         <v>46225.00190693287</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5778,13 +5784,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5794,7 +5800,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B77" s="8">
         <v>46224.89620164352</v>
@@ -5804,7 +5810,7 @@
         <v>46225.00190398148</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -5831,13 +5837,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -5847,7 +5853,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B78" s="5">
         <v>46224.90891903936</v>
@@ -5857,7 +5863,7 @@
         <v>46225.00190130787</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5884,13 +5890,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5900,7 +5906,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B79" s="8">
         <v>46224.90893305556</v>
@@ -5910,7 +5916,7 @@
         <v>46225.00189846064</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -5937,13 +5943,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -5953,7 +5959,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B80" s="5">
         <v>46224.908947303236</v>
@@ -5963,7 +5969,7 @@
         <v>46225.0018940625</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -5990,13 +5996,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6006,7 +6012,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B81" s="8">
         <v>46224.896206122685</v>
@@ -6016,7 +6022,7 @@
         <v>46225.00178723379</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6043,13 +6049,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q81" s="8">
         <v>46286</v>
@@ -6069,7 +6075,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B82" s="5">
         <v>46224.89621025463</v>
@@ -6079,7 +6085,7 @@
         <v>46225.00342317129</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6104,13 +6110,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6120,7 +6126,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B83" s="8">
         <v>46224.89621648148</v>
@@ -6130,7 +6136,7 @@
         <v>46225.00341996527</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6155,13 +6161,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6171,7 +6177,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B84" s="5">
         <v>46224.89622278935</v>
@@ -6181,7 +6187,7 @@
         <v>46225.00341686343</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6206,13 +6212,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6222,7 +6228,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B85" s="8">
         <v>46224.90904761574</v>
@@ -6232,7 +6238,7 @@
         <v>46225.00341435186</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6257,13 +6263,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6273,7 +6279,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B86" s="5">
         <v>46224.90906070602</v>
@@ -6283,7 +6289,7 @@
         <v>46225.003411944446</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6308,13 +6314,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6324,7 +6330,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B87" s="8">
         <v>46224.909074537034</v>
@@ -6334,7 +6340,7 @@
         <v>46225.003407199074</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6359,13 +6365,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -6375,7 +6381,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B88" s="5">
         <v>46224.896228784724</v>
@@ -6385,7 +6391,7 @@
         <v>46225.00178356482</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6412,13 +6418,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q88" s="5">
         <v>46287</v>
@@ -6438,7 +6444,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B89" s="8">
         <v>46224.8962330787</v>
@@ -6448,7 +6454,7 @@
         <v>46225.00360141204</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6475,13 +6481,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6491,7 +6497,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B90" s="5">
         <v>46224.89623854167</v>
@@ -6501,7 +6507,7 @@
         <v>46225.003598587966</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6528,13 +6534,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6544,7 +6550,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B91" s="8">
         <v>46224.89624408565</v>
@@ -6554,7 +6560,7 @@
         <v>46225.00359555555</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6581,13 +6587,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6597,7 +6603,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B92" s="5">
         <v>46224.909162303244</v>
@@ -6607,7 +6613,7 @@
         <v>46225.003592696754</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6634,13 +6640,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6650,7 +6656,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B93" s="8">
         <v>46224.90917530093</v>
@@ -6660,7 +6666,7 @@
         <v>46225.00358984954</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -6687,13 +6693,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -6703,7 +6709,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B94" s="5">
         <v>46224.90918795139</v>
@@ -6713,7 +6719,7 @@
         <v>46225.003585150465</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6740,13 +6746,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6756,7 +6762,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B95" s="8">
         <v>46224.896249224534</v>
@@ -6766,7 +6772,7 @@
         <v>46225.00177993056</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -6793,13 +6799,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q95" s="8">
         <v>46288</v>
@@ -6819,7 +6825,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B96" s="5">
         <v>46224.896253391205</v>
@@ -6829,7 +6835,7 @@
         <v>46225.00380877315</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6856,13 +6862,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6872,7 +6878,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B97" s="8">
         <v>46224.89625857639</v>
@@ -6882,7 +6888,7 @@
         <v>46225.00393450231</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -6909,13 +6915,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -6925,7 +6931,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B98" s="5">
         <v>46224.896263622686</v>
@@ -6935,7 +6941,7 @@
         <v>46225.003931203704</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -6962,13 +6968,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -6978,7 +6984,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B99" s="8">
         <v>46224.90936527778</v>
@@ -6988,7 +6994,7 @@
         <v>46225.003927453705</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7015,13 +7021,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7031,7 +7037,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B100" s="5">
         <v>46224.909378055556</v>
@@ -7041,7 +7047,7 @@
         <v>46225.0039243287</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7068,13 +7074,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7084,7 +7090,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B101" s="8">
         <v>46224.90939565972</v>
@@ -7094,7 +7100,7 @@
         <v>46225.003918993054</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7121,13 +7127,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7137,7 +7143,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B102" s="5">
         <v>46224.89630784722</v>
@@ -7147,7 +7153,7 @@
         <v>46225.00177642361</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7174,13 +7180,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q102" s="5">
         <v>46289</v>
@@ -7200,7 +7206,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B103" s="8">
         <v>46224.89631489583</v>
@@ -7210,7 +7216,7 @@
         <v>46225.004084687505</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7237,13 +7243,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7253,7 +7259,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B104" s="5">
         <v>46224.8963246412</v>
@@ -7263,7 +7269,7 @@
         <v>46225.00408194444</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7290,13 +7296,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7306,7 +7312,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B105" s="8">
         <v>46224.896336412035</v>
@@ -7316,7 +7322,7 @@
         <v>46225.00407914352</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7343,13 +7349,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7359,7 +7365,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B106" s="5">
         <v>46224.90947829861</v>
@@ -7369,7 +7375,7 @@
         <v>46225.00407667824</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7396,13 +7402,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7412,7 +7418,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B107" s="8">
         <v>46224.90949266204</v>
@@ -7422,7 +7428,7 @@
         <v>46225.00407431713</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7449,13 +7455,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7465,7 +7471,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B108" s="5">
         <v>46224.90951107639</v>
@@ -7475,7 +7481,7 @@
         <v>46225.00406917824</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7502,13 +7508,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7518,7 +7524,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B109" s="8">
         <v>46224.896346064816</v>
@@ -7528,7 +7534,7 @@
         <v>46225.001770601855</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -7555,13 +7561,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q109" s="8">
         <v>46293</v>
@@ -7581,7 +7587,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B110" s="5">
         <v>46224.896352627315</v>
@@ -7591,7 +7597,7 @@
         <v>46225.00432578704</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7618,13 +7624,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7634,7 +7640,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B111" s="8">
         <v>46224.896357986116</v>
@@ -7644,7 +7650,7 @@
         <v>46225.00432245371</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -7671,13 +7677,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -7687,7 +7693,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B112" s="5">
         <v>46224.89636417824</v>
@@ -7697,7 +7703,7 @@
         <v>46225.00431880787</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7724,13 +7730,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7740,7 +7746,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B113" s="8">
         <v>46224.90960074074</v>
@@ -7750,7 +7756,7 @@
         <v>46225.00431532407</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -7777,13 +7783,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -7793,7 +7799,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B114" s="5">
         <v>46224.909615729164</v>
@@ -7803,7 +7809,7 @@
         <v>46225.00431230324</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7830,13 +7836,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -7846,7 +7852,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B115" s="8">
         <v>46224.90963084491</v>
@@ -7856,7 +7862,7 @@
         <v>46225.00430677083</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -7883,13 +7889,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -7899,7 +7905,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B116" s="5">
         <v>46224.89636990741</v>
@@ -7909,7 +7915,7 @@
         <v>46224.982246342595</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>25</v>
@@ -7933,7 +7939,7 @@
         <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -7946,7 +7952,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B117" s="8">
         <v>46224.89637483796</v>
@@ -7956,16 +7962,16 @@
         <v>46225.004655902776</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I117" s="8">
         <v>46294</v>
@@ -7983,13 +7989,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q117" s="8">
         <v>46294</v>
@@ -8009,7 +8015,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B118" s="5">
         <v>46224.89638173611</v>
@@ -8019,16 +8025,16 @@
         <v>46225.00456991898</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I118" s="5">
         <v>46294</v>
@@ -8046,13 +8052,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8062,7 +8068,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B119" s="8">
         <v>46224.89638608796</v>
@@ -8072,16 +8078,16 @@
         <v>46225.004566655094</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I119" s="8">
         <v>46294</v>
@@ -8099,13 +8105,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8115,7 +8121,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B120" s="5">
         <v>46224.89639070602</v>
@@ -8125,16 +8131,16 @@
         <v>46225.00456336806</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I120" s="5">
         <v>46294</v>
@@ -8152,13 +8158,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8168,7 +8174,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B121" s="8">
         <v>46224.90972969907</v>
@@ -8178,16 +8184,16 @@
         <v>46225.00456075231</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I121" s="8">
         <v>46294</v>
@@ -8205,13 +8211,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8221,7 +8227,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B122" s="5">
         <v>46224.909745763885</v>
@@ -8231,16 +8237,16 @@
         <v>46225.00455841435</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I122" s="5">
         <v>46294</v>
@@ -8258,13 +8264,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8274,7 +8280,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B123" s="8">
         <v>46224.90976548611</v>
@@ -8284,16 +8290,16 @@
         <v>46225.00455403935</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I123" s="8">
         <v>46294</v>
@@ -8311,13 +8317,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8327,7 +8333,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B124" s="5">
         <v>46224.89639515046</v>
@@ -8337,7 +8343,7 @@
         <v>46225.00487923611</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8364,10 +8370,10 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>26</v>
@@ -8390,7 +8396,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B125" s="8">
         <v>46224.89640211806</v>
@@ -8400,7 +8406,7 @@
         <v>46225.00484849537</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8427,13 +8433,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8443,7 +8449,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B126" s="5">
         <v>46224.896406597225</v>
@@ -8453,7 +8459,7 @@
         <v>46225.00484502315</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8480,13 +8486,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8496,7 +8502,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B127" s="8">
         <v>46224.89641076389</v>
@@ -8506,7 +8512,7 @@
         <v>46225.0048419213</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -8533,13 +8539,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -8549,7 +8555,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B128" s="5">
         <v>46224.90987040509</v>
@@ -8559,7 +8565,7 @@
         <v>46225.00483878472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8586,13 +8592,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8602,7 +8608,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B129" s="8">
         <v>46224.90988407408</v>
@@ -8612,7 +8618,7 @@
         <v>46225.00483302084</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -8639,13 +8645,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -8655,7 +8661,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B130" s="5">
         <v>46224.90989866898</v>
@@ -8665,7 +8671,7 @@
         <v>46225.004831886574</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -8692,13 +8698,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -8708,7 +8714,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B131" s="8">
         <v>46224.896414849536</v>
@@ -8718,16 +8724,16 @@
         <v>46225.00524695602</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I131" s="8">
         <v>46296</v>
@@ -8745,13 +8751,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q131" s="8">
         <v>46296</v>
@@ -8771,7 +8777,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B132" s="5">
         <v>46224.896420833335</v>
@@ -8781,16 +8787,16 @@
         <v>46225.00519546296</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I132" s="5">
         <v>46296</v>
@@ -8808,13 +8814,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -8824,7 +8830,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B133" s="8">
         <v>46224.896425520834</v>
@@ -8834,16 +8840,16 @@
         <v>46225.00519261574</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I133" s="8">
         <v>46296</v>
@@ -8861,13 +8867,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -8877,7 +8883,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B134" s="5">
         <v>46224.89642954861</v>
@@ -8887,16 +8893,16 @@
         <v>46225.00518949074</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I134" s="5">
         <v>46296</v>
@@ -8914,13 +8920,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -8930,7 +8936,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B135" s="8">
         <v>46224.90999299768</v>
@@ -8940,16 +8946,16 @@
         <v>46225.00518663194</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I135" s="8">
         <v>46296</v>
@@ -8967,13 +8973,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -8983,7 +8989,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B136" s="5">
         <v>46224.91000321759</v>
@@ -8993,16 +8999,16 @@
         <v>46225.0051837963</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I136" s="5">
         <v>46296</v>
@@ -9020,13 +9026,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9036,7 +9042,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B137" s="8">
         <v>46224.9100178125</v>
@@ -9046,16 +9052,16 @@
         <v>46225.00517873843</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I137" s="8">
         <v>46296</v>
@@ -9073,13 +9079,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9089,7 +9095,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B138" s="5">
         <v>46224.89648862269</v>
@@ -9099,16 +9105,16 @@
         <v>46225.00560130787</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I138" s="5">
         <v>46297</v>
@@ -9126,13 +9132,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q138" s="5">
         <v>46297</v>
@@ -9152,7 +9158,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B139" s="8">
         <v>46224.89649652778</v>
@@ -9162,16 +9168,16 @@
         <v>46225.00578898148</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I139" s="8">
         <v>46297</v>
@@ -9189,13 +9195,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9205,7 +9211,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B140" s="5">
         <v>46224.896501145835</v>
@@ -9215,16 +9221,16 @@
         <v>46225.00578587963</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I140" s="5">
         <v>46297</v>
@@ -9242,13 +9248,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9258,7 +9264,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B141" s="8">
         <v>46224.89650519676</v>
@@ -9268,16 +9274,16 @@
         <v>46225.005782395834</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I141" s="8">
         <v>46297</v>
@@ -9295,13 +9301,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9311,7 +9317,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B142" s="5">
         <v>46224.91010994213</v>
@@ -9321,16 +9327,16 @@
         <v>46225.00577939815</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I142" s="5">
         <v>46297</v>
@@ -9348,13 +9354,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9364,7 +9370,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B143" s="8">
         <v>46224.910124421294</v>
@@ -9374,16 +9380,16 @@
         <v>46225.00577614583</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I143" s="8">
         <v>46297</v>
@@ -9401,13 +9407,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -9417,7 +9423,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B144" s="5">
         <v>46224.91013965278</v>
@@ -9427,16 +9433,16 @@
         <v>46225.005771516204</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I144" s="5">
         <v>46297</v>
@@ -9454,13 +9460,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9470,7 +9476,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B145" s="8">
         <v>46224.89650905093</v>
@@ -9480,7 +9486,7 @@
         <v>46224.984822025464</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>25</v>
@@ -9504,7 +9510,7 @@
         <v>26</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>26</v>
@@ -9517,7 +9523,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B146" s="5">
         <v>46224.89651261574</v>
@@ -9527,16 +9533,16 @@
         <v>46225.00587975694</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I146" s="5">
         <v>46300</v>
@@ -9554,13 +9560,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q146" s="5">
         <v>46304</v>
@@ -9580,7 +9586,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B147" s="8">
         <v>46224.89652059028</v>
@@ -9590,7 +9596,7 @@
         <v>46224.98672077546</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -9617,13 +9623,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q147" s="8">
         <v>46304</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -3648,7 +3648,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46232.5775528125</v>
+        <v>46234.19694222222</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>137</v>
@@ -3692,8 +3692,8 @@
       <c r="R37" s="9">
         <v>46237</v>
       </c>
-      <c r="S37" s="7" t="s">
-        <v>32</v>
+      <c r="S37" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -463,16 +463,16 @@
     <t xml:space="preserve">Ingenieria y diseñoo:,Plano Definitivos OT 4376 </t>
   </si>
   <si>
+    <t>1216771806162105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Definitivos OT 4376 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria y diseñoo:,Check Planos OT 4376 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216771806162105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Definitivos OT 4376 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria y diseñoo:,Check Planos OT 4376 </t>
   </si>
   <si>
     <t>1216771806169487</t>
@@ -3585,7 +3585,7 @@
         <v>46232.57753737269</v>
       </c>
       <c r="D36" s="5">
-        <v>46232.57755179398</v>
+        <v>46235.17742733796</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>131</v>
@@ -3629,8 +3629,8 @@
       <c r="R36" s="5">
         <v>46230</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>135</v>
+      <c r="S36" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3641,7 +3641,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B37" s="9">
         <v>46224.895948425925</v>
@@ -3651,7 +3651,7 @@
         <v>46234.19694222222</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3684,7 +3684,7 @@
         <v>131</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3693,7 +3693,7 @@
         <v>46237</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>128</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>142</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -271,6 +271,9 @@
     <t>Generación OC corte laser  OT 4376,Propuesta compras:</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
@@ -470,9 +473,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ingenieria y diseñoo:,Check Planos OT 4376 </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216771806169487</t>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46238.4864005787</v>
+        <v>46239.202762789355</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>67</v>
@@ -2540,29 +2540,29 @@
       <c r="R17" s="9">
         <v>46245</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>32</v>
+      <c r="S17" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B18" s="5">
         <v>46224.89582128472</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46238.48639278935</v>
+        <v>46239.202761458335</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2595,7 +2595,7 @@
         <v>69</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q18" s="5">
         <v>46246</v>
@@ -2603,29 +2603,29 @@
       <c r="R18" s="5">
         <v>46245</v>
       </c>
-      <c r="S18" s="7" t="s">
-        <v>32</v>
+      <c r="S18" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" s="9">
         <v>46224.89582549769</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46238.486392245366</v>
+        <v>46239.20276144676</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2658,7 +2658,7 @@
         <v>69</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q19" s="9">
         <v>46246</v>
@@ -2666,29 +2666,29 @@
       <c r="R19" s="9">
         <v>46245</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>32</v>
+      <c r="S19" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
       <c r="U19" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="5">
         <v>46224.8958294676</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46238.48639236111</v>
+        <v>46239.20276144676</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2721,7 +2721,7 @@
         <v>69</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q20" s="5">
         <v>46246</v>
@@ -2729,19 +2729,19 @@
       <c r="R20" s="5">
         <v>46245</v>
       </c>
-      <c r="S20" s="7" t="s">
-        <v>32</v>
+      <c r="S20" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
       <c r="U20" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B21" s="9">
         <v>46224.89570832176</v>
@@ -2751,7 +2751,7 @@
         <v>46224.97302240741</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -2775,7 +2775,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" s="5">
         <v>46224.89583418981</v>
@@ -2798,16 +2798,16 @@
         <v>46224.98711915509</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I22" s="5">
         <v>46247</v>
@@ -2825,13 +2825,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q22" s="5">
         <v>46259</v>
@@ -2846,12 +2846,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="9">
         <v>46224.895839062505</v>
@@ -2861,16 +2861,16 @@
         <v>46224.98722679398</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I23" s="9">
         <v>46247</v>
@@ -2888,13 +2888,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>67</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2905,12 +2905,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46224.8958440162</v>
@@ -2920,16 +2920,16 @@
         <v>46224.98722206018</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I24" s="5">
         <v>46251</v>
@@ -2947,13 +2947,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2964,12 +2964,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B25" s="9">
         <v>46224.89584935185</v>
@@ -2979,16 +2979,16 @@
         <v>46224.987115104166</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I25" s="9">
         <v>46247</v>
@@ -3006,10 +3006,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3027,12 +3027,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5">
         <v>46224.895853553244</v>
@@ -3042,16 +3042,16 @@
         <v>46224.98733012732</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I26" s="5">
         <v>46247</v>
@@ -3069,13 +3069,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3085,7 +3085,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" s="9">
         <v>46224.895863321755</v>
@@ -3095,16 +3095,16 @@
         <v>46224.987326828705</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I27" s="9">
         <v>46251</v>
@@ -3122,13 +3122,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5">
         <v>46224.89586804398</v>
@@ -3148,16 +3148,16 @@
         <v>46224.98710894676</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -3175,10 +3175,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3196,12 +3196,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" s="9">
         <v>46224.895871886576</v>
@@ -3211,16 +3211,16 @@
         <v>46224.98742798611</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I29" s="9">
         <v>46247</v>
@@ -3238,13 +3238,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" s="5">
         <v>46224.89587627315</v>
@@ -3264,16 +3264,16 @@
         <v>46224.987424872685</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I30" s="5">
         <v>46251</v>
@@ -3291,13 +3291,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3307,7 +3307,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" s="9">
         <v>46224.89588070602</v>
@@ -3317,16 +3317,16 @@
         <v>46224.9875411574</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3344,10 +3344,10 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -3365,12 +3365,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46224.89592390046</v>
@@ -3380,16 +3380,16 @@
         <v>46237.55371252315</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I32" s="5">
         <v>46247</v>
@@ -3407,13 +3407,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" s="9">
         <v>46224.89592935186</v>
@@ -3433,16 +3433,16 @@
         <v>46224.987624201385</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I33" s="9">
         <v>46258</v>
@@ -3460,13 +3460,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3476,7 +3476,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46224.89593387731</v>
@@ -3486,16 +3486,16 @@
         <v>46224.98774165509</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3513,13 +3513,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3529,7 +3529,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" s="9">
         <v>46224.89593827546</v>
@@ -3539,7 +3539,7 @@
         <v>46238.486380925926</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3563,7 +3563,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3576,7 +3576,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46224.895942546296</v>
@@ -3588,16 +3588,16 @@
         <v>46235.17742733796</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3615,13 +3615,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3641,7 +3641,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B37" s="9">
         <v>46224.895948425925</v>
@@ -3653,16 +3653,16 @@
         <v>46238.486330914355</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3680,13 +3680,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3695,7 +3695,7 @@
         <v>46237</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="T37" s="10">
         <v>1</v>
@@ -3745,10 +3745,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>142</v>
@@ -3760,7 +3760,7 @@
         <v>46244</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>
@@ -3808,13 +3808,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>147</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4225,7 +4225,7 @@
         <v>158</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>164</v>
@@ -4243,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4288,7 +4288,7 @@
         <v>158</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>167</v>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4351,7 +4351,7 @@
         <v>158</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>170</v>
@@ -4369,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4390,10 +4390,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I50" s="5">
         <v>46261</v>
@@ -4432,7 +4432,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4453,10 +4453,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I51" s="9">
         <v>46261</v>
@@ -4495,7 +4495,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4516,10 +4516,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I52" s="5">
         <v>46261</v>
@@ -4558,7 +4558,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4620,7 +4620,7 @@
         <v>46224.98900751157</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4650,7 +4650,7 @@
         <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>186</v>
@@ -4668,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="U54" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4683,7 +4683,7 @@
         <v>46224.98900451389</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4773,7 +4773,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>189</v>
@@ -4826,7 +4826,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>192</v>
@@ -4879,7 +4879,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>195</v>
@@ -4932,10 +4932,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>193</v>
@@ -4985,10 +4985,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>193</v>
@@ -5038,10 +5038,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>199</v>
@@ -5070,10 +5070,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5112,7 +5112,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5133,10 +5133,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I63" s="9">
         <v>46274</v>
@@ -5186,10 +5186,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I64" s="5">
         <v>46274</v>
@@ -5239,10 +5239,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I65" s="9">
         <v>46274</v>
@@ -5292,10 +5292,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I66" s="5">
         <v>46274</v>
@@ -5345,10 +5345,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I67" s="9">
         <v>46274</v>
@@ -5398,10 +5398,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5540,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5603,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5666,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5776,7 +5776,7 @@
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6157,7 +6157,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6526,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6907,7 +6907,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="U102" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8097,7 +8097,7 @@
         <v>0</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -8478,7 +8478,7 @@
         <v>0</v>
       </c>
       <c r="U124" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="U131" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
@@ -9240,7 +9240,7 @@
         <v>0</v>
       </c>
       <c r="U138" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
@@ -9668,7 +9668,7 @@
         <v>0</v>
       </c>
       <c r="U146" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
@@ -9731,7 +9731,7 @@
         <v>0</v>
       </c>
       <c r="U147" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -3650,7 +3650,7 @@
         <v>46238.48631474537</v>
       </c>
       <c r="D37" s="9">
-        <v>46238.486330914355</v>
+        <v>46242.177803032406</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>137</v>
@@ -3694,8 +3694,8 @@
       <c r="R37" s="9">
         <v>46237</v>
       </c>
-      <c r="S37" s="12" t="s">
-        <v>71</v>
+      <c r="S37" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T37" s="10">
         <v>1</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="346">
   <si>
     <t>50001577- "XEMORTIZ LA CANTERA"</t>
   </si>
@@ -269,9 +269,6 @@
   </si>
   <si>
     <t>Generación OC corte laser  OT 4376,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>Tarea en curso</t>
@@ -2496,7 +2493,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46246.250919143524</v>
+        <v>46247.200885451384</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>67</v>
@@ -2540,29 +2537,29 @@
       <c r="R17" s="9">
         <v>46245</v>
       </c>
-      <c r="S17" s="12" t="s">
-        <v>71</v>
+      <c r="S17" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5">
         <v>46224.89582128472</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46246.25091673611</v>
+        <v>46247.200884826394</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2595,7 +2592,7 @@
         <v>69</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="5">
         <v>46246</v>
@@ -2603,29 +2600,29 @@
       <c r="R18" s="5">
         <v>46245</v>
       </c>
-      <c r="S18" s="12" t="s">
-        <v>71</v>
+      <c r="S18" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" s="9">
         <v>46224.89582549769</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46246.25091795139</v>
+        <v>46247.200885659724</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2658,7 +2655,7 @@
         <v>69</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q19" s="9">
         <v>46246</v>
@@ -2666,29 +2663,29 @@
       <c r="R19" s="9">
         <v>46245</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>71</v>
+      <c r="S19" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
       <c r="U19" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B20" s="5">
         <v>46224.8958294676</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46246.25091475694</v>
+        <v>46247.200884826394</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2721,7 +2718,7 @@
         <v>69</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q20" s="5">
         <v>46246</v>
@@ -2729,19 +2726,19 @@
       <c r="R20" s="5">
         <v>46245</v>
       </c>
-      <c r="S20" s="12" t="s">
-        <v>71</v>
+      <c r="S20" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
       <c r="U20" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B21" s="9">
         <v>46224.89570832176</v>
@@ -2751,7 +2748,7 @@
         <v>46224.97302240741</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -2775,7 +2772,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -2788,7 +2785,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B22" s="5">
         <v>46224.89583418981</v>
@@ -2798,16 +2795,16 @@
         <v>46224.98711915509</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="I22" s="5">
         <v>46247</v>
@@ -2825,13 +2822,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q22" s="5">
         <v>46259</v>
@@ -2846,12 +2843,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B23" s="9">
         <v>46224.895839062505</v>
@@ -2861,16 +2858,16 @@
         <v>46224.98722679398</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="I23" s="9">
         <v>46247</v>
@@ -2888,13 +2885,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>67</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2905,12 +2902,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5">
         <v>46224.8958440162</v>
@@ -2920,16 +2917,16 @@
         <v>46224.98722206018</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="I24" s="5">
         <v>46251</v>
@@ -2947,13 +2944,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2964,12 +2961,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B25" s="9">
         <v>46224.89584935185</v>
@@ -2979,16 +2976,16 @@
         <v>46224.987115104166</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="I25" s="9">
         <v>46247</v>
@@ -3006,10 +3003,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3027,12 +3024,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" s="5">
         <v>46224.895853553244</v>
@@ -3042,16 +3039,16 @@
         <v>46224.98733012732</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="I26" s="5">
         <v>46247</v>
@@ -3069,13 +3066,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3085,7 +3082,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="9">
         <v>46224.895863321755</v>
@@ -3095,16 +3092,16 @@
         <v>46224.987326828705</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="I27" s="9">
         <v>46251</v>
@@ -3122,13 +3119,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3138,7 +3135,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46224.89586804398</v>
@@ -3148,16 +3145,16 @@
         <v>46224.98710894676</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -3175,10 +3172,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3196,12 +3193,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B29" s="9">
         <v>46224.895871886576</v>
@@ -3211,16 +3208,16 @@
         <v>46224.98742798611</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="I29" s="9">
         <v>46247</v>
@@ -3238,13 +3235,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3254,7 +3251,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B30" s="5">
         <v>46224.89587627315</v>
@@ -3264,16 +3261,16 @@
         <v>46224.987424872685</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="I30" s="5">
         <v>46251</v>
@@ -3291,13 +3288,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3307,7 +3304,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B31" s="9">
         <v>46224.89588070602</v>
@@ -3317,16 +3314,16 @@
         <v>46224.9875411574</v>
       </c>
       <c r="E31" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
+      <c r="H31" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3344,10 +3341,10 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -3365,12 +3362,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46224.89592390046</v>
@@ -3380,16 +3377,16 @@
         <v>46237.55371252315</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="I32" s="5">
         <v>46247</v>
@@ -3407,13 +3404,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O32" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P32" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3423,7 +3420,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B33" s="9">
         <v>46224.89592935186</v>
@@ -3433,16 +3430,16 @@
         <v>46224.987624201385</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="I33" s="9">
         <v>46258</v>
@@ -3460,13 +3457,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3476,7 +3473,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46224.89593387731</v>
@@ -3486,16 +3483,16 @@
         <v>46224.98774165509</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3513,13 +3510,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3529,7 +3526,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B35" s="9">
         <v>46224.89593827546</v>
@@ -3539,7 +3536,7 @@
         <v>46238.486380925926</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3563,7 +3560,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3576,7 +3573,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B36" s="5">
         <v>46224.895942546296</v>
@@ -3588,16 +3585,16 @@
         <v>46235.17742733796</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3615,13 +3612,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3641,7 +3638,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B37" s="9">
         <v>46224.895948425925</v>
@@ -3653,16 +3650,16 @@
         <v>46242.177803032406</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>134</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3680,13 +3677,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3706,7 +3703,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46224.895953506944</v>
@@ -3724,10 +3721,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3745,13 +3742,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3771,7 +3768,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B39" s="9">
         <v>46224.89596851852</v>
@@ -3781,16 +3778,16 @@
         <v>46224.9887275463</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="I39" s="9">
         <v>46290</v>
@@ -3808,13 +3805,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3829,12 +3826,12 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46224.89597322917</v>
@@ -3844,16 +3841,16 @@
         <v>46224.98802077546</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3869,13 +3866,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="P40" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="P40" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3885,7 +3882,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B41" s="9">
         <v>46224.89597747685</v>
@@ -3895,16 +3892,16 @@
         <v>46224.988017592594</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3920,13 +3917,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3936,7 +3933,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46224.89600425926</v>
@@ -3946,16 +3943,16 @@
         <v>46224.98801423611</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -3971,13 +3968,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O42" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3987,7 +3984,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B43" s="9">
         <v>46224.90846989583</v>
@@ -3997,16 +3994,16 @@
         <v>46224.988011203706</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="9">
@@ -4022,13 +4019,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O43" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="P43" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="P43" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4038,7 +4035,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B44" s="5">
         <v>46224.908482824074</v>
@@ -4048,16 +4045,16 @@
         <v>46224.98800859954</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -4073,13 +4070,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O44" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4089,7 +4086,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B45" s="9">
         <v>46224.908498171295</v>
@@ -4099,16 +4096,16 @@
         <v>46224.98800302083</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="9">
@@ -4124,13 +4121,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O45" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="P45" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="P45" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4140,7 +4137,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B46" s="5">
         <v>46224.89600854166</v>
@@ -4150,7 +4147,7 @@
         <v>46224.97705253473</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4174,7 +4171,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4187,7 +4184,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B47" s="9">
         <v>46224.896012384255</v>
@@ -4197,16 +4194,16 @@
         <v>46224.9888250463</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="9">
@@ -4222,13 +4219,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q47" s="9">
         <v>46260</v>
@@ -4243,12 +4240,12 @@
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B48" s="5">
         <v>46224.896018368054</v>
@@ -4258,16 +4255,16 @@
         <v>46224.98882244213</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I48" s="5">
         <v>46260</v>
@@ -4285,13 +4282,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q48" s="5">
         <v>46260</v>
@@ -4306,12 +4303,12 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B49" s="9">
         <v>46224.89602424769</v>
@@ -4321,16 +4318,16 @@
         <v>46224.98881765046</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I49" s="9">
         <v>46260</v>
@@ -4348,13 +4345,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q49" s="9">
         <v>46260</v>
@@ -4369,12 +4366,12 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B50" s="5">
         <v>46224.89603097222</v>
@@ -4384,16 +4381,16 @@
         <v>46224.98890766204</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I50" s="5">
         <v>46261</v>
@@ -4411,13 +4408,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q50" s="5">
         <v>46261</v>
@@ -4432,12 +4429,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B51" s="9">
         <v>46224.89603738426</v>
@@ -4447,16 +4444,16 @@
         <v>46224.9889028125</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="I51" s="9">
         <v>46261</v>
@@ -4474,13 +4471,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q51" s="9">
         <v>46261</v>
@@ -4495,12 +4492,12 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B52" s="5">
         <v>46224.89604363426</v>
@@ -4510,16 +4507,16 @@
         <v>46224.988900625</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I52" s="5">
         <v>46261</v>
@@ -4537,13 +4534,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q52" s="5">
         <v>46261</v>
@@ -4558,12 +4555,12 @@
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B53" s="9">
         <v>46224.89604989583</v>
@@ -4573,7 +4570,7 @@
         <v>46224.978400416665</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4597,7 +4594,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4610,7 +4607,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B54" s="5">
         <v>46224.8960534375</v>
@@ -4620,16 +4617,16 @@
         <v>46224.98900751157</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46262</v>
@@ -4647,13 +4644,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q54" s="5">
         <v>46266</v>
@@ -4668,12 +4665,12 @@
         <v>0</v>
       </c>
       <c r="U54" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B55" s="9">
         <v>46224.89605969907</v>
@@ -4683,16 +4680,16 @@
         <v>46224.98900451389</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I55" s="9">
         <v>46267</v>
@@ -4710,13 +4707,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q55" s="9">
         <v>46273</v>
@@ -4731,12 +4728,12 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B56" s="5">
         <v>46224.89606466435</v>
@@ -4746,16 +4743,16 @@
         <v>46238.48636976852</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I56" s="5">
         <v>46267</v>
@@ -4773,13 +4770,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4789,7 +4786,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B57" s="9">
         <v>46224.89607361111</v>
@@ -4799,16 +4796,16 @@
         <v>46238.4863703588</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I57" s="9">
         <v>46267</v>
@@ -4826,13 +4823,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O57" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P57" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4842,7 +4839,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B58" s="5">
         <v>46224.89613331019</v>
@@ -4852,16 +4849,16 @@
         <v>46238.48638123843</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I58" s="5">
         <v>46267</v>
@@ -4879,13 +4876,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4895,7 +4892,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B59" s="9">
         <v>46224.90866162037</v>
@@ -4905,16 +4902,16 @@
         <v>46224.992584293985</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I59" s="9">
         <v>46267</v>
@@ -4932,13 +4929,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4948,7 +4945,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B60" s="5">
         <v>46224.90867304398</v>
@@ -4958,16 +4955,16 @@
         <v>46224.99258355324</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I60" s="5">
         <v>46267</v>
@@ -4985,13 +4982,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5001,7 +4998,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B61" s="9">
         <v>46224.90868626157</v>
@@ -5011,16 +5008,16 @@
         <v>46224.99258276621</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I61" s="9">
         <v>46267</v>
@@ -5038,13 +5035,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5054,7 +5051,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B62" s="5">
         <v>46224.89614391203</v>
@@ -5064,16 +5061,16 @@
         <v>46225.00135394676</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5091,13 +5088,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q62" s="5">
         <v>46274</v>
@@ -5112,12 +5109,12 @@
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B63" s="9">
         <v>46224.896148935186</v>
@@ -5127,16 +5124,16 @@
         <v>46238.486370949075</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="I63" s="9">
         <v>46274</v>
@@ -5154,13 +5151,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>204</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>205</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5170,7 +5167,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B64" s="5">
         <v>46224.89615454861</v>
@@ -5180,16 +5177,16 @@
         <v>46238.486371377316</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I64" s="5">
         <v>46274</v>
@@ -5207,13 +5204,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5223,7 +5220,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B65" s="9">
         <v>46224.89616001157</v>
@@ -5233,16 +5230,16 @@
         <v>46238.486371782405</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="I65" s="9">
         <v>46274</v>
@@ -5260,13 +5257,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>204</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>205</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5276,7 +5273,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B66" s="5">
         <v>46224.90877734954</v>
@@ -5286,16 +5283,16 @@
         <v>46225.00151444445</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I66" s="5">
         <v>46274</v>
@@ -5313,13 +5310,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5329,7 +5326,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B67" s="9">
         <v>46224.90879113426</v>
@@ -5339,16 +5336,16 @@
         <v>46225.00151381944</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="I67" s="9">
         <v>46274</v>
@@ -5366,13 +5363,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5382,7 +5379,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B68" s="5">
         <v>46224.90880622686</v>
@@ -5392,16 +5389,16 @@
         <v>46225.001513020834</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5419,13 +5416,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5435,7 +5432,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B69" s="9">
         <v>46224.89616483796</v>
@@ -5445,7 +5442,7 @@
         <v>46224.97892864583</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>25</v>
@@ -5469,7 +5466,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>26</v>
@@ -5482,7 +5479,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B70" s="5">
         <v>46224.89616836805</v>
@@ -5492,16 +5489,16 @@
         <v>46232.190274444445</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I70" s="5">
         <v>46230</v>
@@ -5519,13 +5516,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>54</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q70" s="5">
         <v>46231</v>
@@ -5540,12 +5537,12 @@
         <v>0</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B71" s="9">
         <v>46224.89617388889</v>
@@ -5555,16 +5552,16 @@
         <v>46232.19027465278</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I71" s="9">
         <v>46230</v>
@@ -5582,13 +5579,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q71" s="9">
         <v>46231</v>
@@ -5603,12 +5600,12 @@
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B72" s="5">
         <v>46224.89617931713</v>
@@ -5618,16 +5615,16 @@
         <v>46232.19027490741</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I72" s="5">
         <v>46230</v>
@@ -5645,13 +5642,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -5666,12 +5663,12 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B73" s="9">
         <v>46224.896184826386</v>
@@ -5681,7 +5678,7 @@
         <v>46224.981535706014</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>25</v>
@@ -5705,7 +5702,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5718,7 +5715,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B74" s="5">
         <v>46224.89618846065</v>
@@ -5728,7 +5725,7 @@
         <v>46225.00179069444</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5755,13 +5752,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q74" s="5">
         <v>46281</v>
@@ -5776,12 +5773,12 @@
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B75" s="9">
         <v>46224.89619313658</v>
@@ -5791,7 +5788,7 @@
         <v>46225.00190993056</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5818,13 +5815,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5834,7 +5831,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B76" s="5">
         <v>46224.89619747685</v>
@@ -5844,7 +5841,7 @@
         <v>46225.00190693287</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5871,13 +5868,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5887,7 +5884,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B77" s="9">
         <v>46224.89620164352</v>
@@ -5897,7 +5894,7 @@
         <v>46225.00190398148</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5924,13 +5921,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5940,7 +5937,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B78" s="5">
         <v>46224.90891903936</v>
@@ -5950,7 +5947,7 @@
         <v>46225.00190130787</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5977,13 +5974,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5993,7 +5990,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B79" s="9">
         <v>46224.90893305556</v>
@@ -6003,7 +6000,7 @@
         <v>46225.00189846064</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6030,13 +6027,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6046,7 +6043,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B80" s="5">
         <v>46224.908947303236</v>
@@ -6056,7 +6053,7 @@
         <v>46225.0018940625</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6083,13 +6080,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6099,7 +6096,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B81" s="9">
         <v>46224.896206122685</v>
@@ -6109,7 +6106,7 @@
         <v>46225.00178723379</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6136,13 +6133,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q81" s="9">
         <v>46286</v>
@@ -6157,12 +6154,12 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B82" s="5">
         <v>46224.89621025463</v>
@@ -6172,7 +6169,7 @@
         <v>46238.48638170139</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6197,13 +6194,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6213,7 +6210,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B83" s="9">
         <v>46224.89621648148</v>
@@ -6223,7 +6220,7 @@
         <v>46238.486382233794</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6248,13 +6245,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O83" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="P83" s="10" t="s">
         <v>241</v>
-      </c>
-      <c r="P83" s="10" t="s">
-        <v>242</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6264,7 +6261,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B84" s="5">
         <v>46224.89622278935</v>
@@ -6274,7 +6271,7 @@
         <v>46238.486382800926</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6299,13 +6296,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6315,7 +6312,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B85" s="9">
         <v>46224.90904761574</v>
@@ -6325,7 +6322,7 @@
         <v>46225.00341435186</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6350,13 +6347,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6366,7 +6363,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B86" s="5">
         <v>46224.90906070602</v>
@@ -6376,7 +6373,7 @@
         <v>46225.003411944446</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6401,13 +6398,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6417,7 +6414,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B87" s="9">
         <v>46224.909074537034</v>
@@ -6427,7 +6424,7 @@
         <v>46225.003407199074</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6452,13 +6449,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6468,7 +6465,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B88" s="5">
         <v>46224.896228784724</v>
@@ -6478,7 +6475,7 @@
         <v>46225.00178356482</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6505,13 +6502,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q88" s="5">
         <v>46287</v>
@@ -6526,12 +6523,12 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B89" s="9">
         <v>46224.8962330787</v>
@@ -6541,7 +6538,7 @@
         <v>46225.00360141204</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6568,13 +6565,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6584,7 +6581,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B90" s="5">
         <v>46224.89623854167</v>
@@ -6594,7 +6591,7 @@
         <v>46225.003598587966</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6621,13 +6618,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6637,7 +6634,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B91" s="9">
         <v>46224.89624408565</v>
@@ -6647,7 +6644,7 @@
         <v>46225.00359555555</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6674,13 +6671,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6690,7 +6687,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B92" s="5">
         <v>46224.909162303244</v>
@@ -6700,7 +6697,7 @@
         <v>46225.003592696754</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6727,13 +6724,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6743,7 +6740,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B93" s="9">
         <v>46224.90917530093</v>
@@ -6753,7 +6750,7 @@
         <v>46225.00358984954</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6780,13 +6777,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6796,7 +6793,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B94" s="5">
         <v>46224.90918795139</v>
@@ -6806,7 +6803,7 @@
         <v>46225.003585150465</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6833,13 +6830,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6849,7 +6846,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B95" s="9">
         <v>46224.896249224534</v>
@@ -6859,7 +6856,7 @@
         <v>46225.00177993056</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6886,13 +6883,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q95" s="9">
         <v>46288</v>
@@ -6907,12 +6904,12 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B96" s="5">
         <v>46224.896253391205</v>
@@ -6922,7 +6919,7 @@
         <v>46238.48637237269</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6949,13 +6946,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O96" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="P96" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6965,7 +6962,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B97" s="9">
         <v>46224.89625857639</v>
@@ -6975,7 +6972,7 @@
         <v>46238.486383379626</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7002,13 +6999,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O97" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="P97" s="10" t="s">
         <v>264</v>
-      </c>
-      <c r="P97" s="10" t="s">
-        <v>265</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7018,7 +7015,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B98" s="5">
         <v>46224.896263622686</v>
@@ -7028,7 +7025,7 @@
         <v>46225.003931203704</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7055,13 +7052,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O98" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="P98" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7071,7 +7068,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B99" s="9">
         <v>46224.90936527778</v>
@@ -7081,7 +7078,7 @@
         <v>46225.003927453705</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7108,13 +7105,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7124,7 +7121,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B100" s="5">
         <v>46224.909378055556</v>
@@ -7134,7 +7131,7 @@
         <v>46225.0039243287</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7161,13 +7158,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7177,7 +7174,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B101" s="9">
         <v>46224.90939565972</v>
@@ -7187,7 +7184,7 @@
         <v>46225.003918993054</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7214,13 +7211,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7230,7 +7227,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B102" s="5">
         <v>46224.89630784722</v>
@@ -7240,7 +7237,7 @@
         <v>46225.00177642361</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7267,13 +7264,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q102" s="5">
         <v>46289</v>
@@ -7288,12 +7285,12 @@
         <v>0</v>
       </c>
       <c r="U102" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B103" s="9">
         <v>46224.89631489583</v>
@@ -7303,7 +7300,7 @@
         <v>46225.004084687505</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7330,13 +7327,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O103" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="P103" s="10" t="s">
         <v>276</v>
-      </c>
-      <c r="P103" s="10" t="s">
-        <v>277</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7346,7 +7343,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B104" s="5">
         <v>46224.8963246412</v>
@@ -7356,7 +7353,7 @@
         <v>46225.00408194444</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7383,13 +7380,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O104" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="P104" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7399,7 +7396,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B105" s="9">
         <v>46224.896336412035</v>
@@ -7409,7 +7406,7 @@
         <v>46225.00407914352</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7436,13 +7433,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O105" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="P105" s="10" t="s">
         <v>276</v>
-      </c>
-      <c r="P105" s="10" t="s">
-        <v>277</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7452,7 +7449,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B106" s="5">
         <v>46224.90947829861</v>
@@ -7462,7 +7459,7 @@
         <v>46225.00407667824</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7489,13 +7486,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7505,7 +7502,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B107" s="9">
         <v>46224.90949266204</v>
@@ -7515,7 +7512,7 @@
         <v>46225.00407431713</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7542,13 +7539,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7558,7 +7555,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B108" s="5">
         <v>46224.90951107639</v>
@@ -7568,7 +7565,7 @@
         <v>46225.00406917824</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7595,13 +7592,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7611,7 +7608,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B109" s="9">
         <v>46224.896346064816</v>
@@ -7621,7 +7618,7 @@
         <v>46225.001770601855</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7648,13 +7645,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q109" s="9">
         <v>46293</v>
@@ -7669,12 +7666,12 @@
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B110" s="5">
         <v>46224.896352627315</v>
@@ -7684,7 +7681,7 @@
         <v>46225.00432578704</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7711,13 +7708,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7727,7 +7724,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B111" s="9">
         <v>46224.896357986116</v>
@@ -7737,7 +7734,7 @@
         <v>46225.00432245371</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7764,13 +7761,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7780,7 +7777,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B112" s="5">
         <v>46224.89636417824</v>
@@ -7790,7 +7787,7 @@
         <v>46225.00431880787</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7817,13 +7814,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7833,7 +7830,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B113" s="9">
         <v>46224.90960074074</v>
@@ -7843,7 +7840,7 @@
         <v>46225.00431532407</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -7870,13 +7867,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7886,7 +7883,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B114" s="5">
         <v>46224.909615729164</v>
@@ -7896,7 +7893,7 @@
         <v>46225.00431230324</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7923,13 +7920,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -7939,7 +7936,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B115" s="9">
         <v>46224.90963084491</v>
@@ -7949,7 +7946,7 @@
         <v>46225.00430677083</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -7976,13 +7973,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -7992,7 +7989,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B116" s="5">
         <v>46224.89636990741</v>
@@ -8002,7 +7999,7 @@
         <v>46224.982246342595</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>25</v>
@@ -8026,7 +8023,7 @@
         <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -8039,7 +8036,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B117" s="9">
         <v>46224.89637483796</v>
@@ -8049,16 +8046,16 @@
         <v>46225.004655902776</v>
       </c>
       <c r="E117" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="F117" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G117" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="F117" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G117" s="10" t="s">
+      <c r="H117" s="10" t="s">
         <v>298</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>299</v>
       </c>
       <c r="I117" s="9">
         <v>46294</v>
@@ -8076,13 +8073,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q117" s="9">
         <v>46294</v>
@@ -8097,12 +8094,12 @@
         <v>0</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B118" s="5">
         <v>46224.89638173611</v>
@@ -8112,16 +8109,16 @@
         <v>46225.00456991898</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>298</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>299</v>
       </c>
       <c r="I118" s="5">
         <v>46294</v>
@@ -8139,13 +8136,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8155,7 +8152,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B119" s="9">
         <v>46224.89638608796</v>
@@ -8165,16 +8162,16 @@
         <v>46225.004566655094</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="H119" s="10" t="s">
         <v>298</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>299</v>
       </c>
       <c r="I119" s="9">
         <v>46294</v>
@@ -8192,13 +8189,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8208,7 +8205,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B120" s="5">
         <v>46224.89639070602</v>
@@ -8218,16 +8215,16 @@
         <v>46225.00456336806</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>298</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>299</v>
       </c>
       <c r="I120" s="5">
         <v>46294</v>
@@ -8245,13 +8242,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8261,7 +8258,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B121" s="9">
         <v>46224.90972969907</v>
@@ -8271,16 +8268,16 @@
         <v>46225.00456075231</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="H121" s="10" t="s">
         <v>298</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>299</v>
       </c>
       <c r="I121" s="9">
         <v>46294</v>
@@ -8298,13 +8295,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8314,7 +8311,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B122" s="5">
         <v>46224.909745763885</v>
@@ -8324,16 +8321,16 @@
         <v>46225.00455841435</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>298</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>299</v>
       </c>
       <c r="I122" s="5">
         <v>46294</v>
@@ -8351,13 +8348,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8367,7 +8364,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B123" s="9">
         <v>46224.90976548611</v>
@@ -8377,16 +8374,16 @@
         <v>46225.00455403935</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="H123" s="10" t="s">
         <v>298</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>299</v>
       </c>
       <c r="I123" s="9">
         <v>46294</v>
@@ -8404,13 +8401,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8420,7 +8417,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B124" s="5">
         <v>46224.89639515046</v>
@@ -8430,7 +8427,7 @@
         <v>46225.00487923611</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8457,10 +8454,10 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>26</v>
@@ -8478,12 +8475,12 @@
         <v>0</v>
       </c>
       <c r="U124" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B125" s="9">
         <v>46224.89640211806</v>
@@ -8493,7 +8490,7 @@
         <v>46225.00484849537</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8520,13 +8517,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8536,7 +8533,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B126" s="5">
         <v>46224.896406597225</v>
@@ -8546,7 +8543,7 @@
         <v>46225.00484502315</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8573,13 +8570,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8589,7 +8586,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B127" s="9">
         <v>46224.89641076389</v>
@@ -8599,7 +8596,7 @@
         <v>46225.0048419213</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -8626,13 +8623,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8642,7 +8639,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B128" s="5">
         <v>46224.90987040509</v>
@@ -8652,7 +8649,7 @@
         <v>46225.00483878472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8679,13 +8676,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8695,7 +8692,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B129" s="9">
         <v>46224.90988407408</v>
@@ -8705,7 +8702,7 @@
         <v>46225.00483302084</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8732,13 +8729,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8748,7 +8745,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B130" s="5">
         <v>46224.90989866898</v>
@@ -8758,7 +8755,7 @@
         <v>46225.004831886574</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -8785,13 +8782,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -8801,7 +8798,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B131" s="9">
         <v>46224.896414849536</v>
@@ -8811,16 +8808,16 @@
         <v>46225.00524695602</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I131" s="9">
         <v>46296</v>
@@ -8838,13 +8835,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q131" s="9">
         <v>46296</v>
@@ -8859,12 +8856,12 @@
         <v>0</v>
       </c>
       <c r="U131" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B132" s="5">
         <v>46224.896420833335</v>
@@ -8874,16 +8871,16 @@
         <v>46225.00519546296</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I132" s="5">
         <v>46296</v>
@@ -8901,13 +8898,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -8917,7 +8914,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B133" s="9">
         <v>46224.896425520834</v>
@@ -8927,16 +8924,16 @@
         <v>46225.00519261574</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I133" s="9">
         <v>46296</v>
@@ -8954,13 +8951,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -8970,7 +8967,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B134" s="5">
         <v>46224.89642954861</v>
@@ -8980,16 +8977,16 @@
         <v>46225.00518949074</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I134" s="5">
         <v>46296</v>
@@ -9007,13 +9004,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9023,7 +9020,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B135" s="9">
         <v>46224.90999299768</v>
@@ -9033,16 +9030,16 @@
         <v>46225.00518663194</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H135" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I135" s="9">
         <v>46296</v>
@@ -9060,13 +9057,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9076,7 +9073,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B136" s="5">
         <v>46224.91000321759</v>
@@ -9086,16 +9083,16 @@
         <v>46225.0051837963</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I136" s="5">
         <v>46296</v>
@@ -9113,13 +9110,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9129,7 +9126,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B137" s="9">
         <v>46224.9100178125</v>
@@ -9139,16 +9136,16 @@
         <v>46225.00517873843</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H137" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H137" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I137" s="9">
         <v>46296</v>
@@ -9166,13 +9163,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9182,7 +9179,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B138" s="5">
         <v>46224.89648862269</v>
@@ -9192,16 +9189,16 @@
         <v>46225.00560130787</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I138" s="5">
         <v>46297</v>
@@ -9219,13 +9216,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q138" s="5">
         <v>46297</v>
@@ -9240,12 +9237,12 @@
         <v>0</v>
       </c>
       <c r="U138" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B139" s="9">
         <v>46224.89649652778</v>
@@ -9255,16 +9252,16 @@
         <v>46225.00578898148</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H139" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H139" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I139" s="9">
         <v>46297</v>
@@ -9282,13 +9279,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9298,7 +9295,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B140" s="5">
         <v>46224.896501145835</v>
@@ -9308,16 +9305,16 @@
         <v>46225.00578587963</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I140" s="5">
         <v>46297</v>
@@ -9335,13 +9332,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9351,7 +9348,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B141" s="9">
         <v>46224.89650519676</v>
@@ -9361,16 +9358,16 @@
         <v>46225.005782395834</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H141" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H141" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I141" s="9">
         <v>46297</v>
@@ -9388,13 +9385,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9404,7 +9401,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B142" s="5">
         <v>46224.91010994213</v>
@@ -9414,16 +9411,16 @@
         <v>46225.00577939815</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I142" s="5">
         <v>46297</v>
@@ -9441,13 +9438,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9457,7 +9454,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B143" s="9">
         <v>46224.910124421294</v>
@@ -9467,16 +9464,16 @@
         <v>46225.00577614583</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H143" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I143" s="9">
         <v>46297</v>
@@ -9494,13 +9491,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9510,7 +9507,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B144" s="5">
         <v>46224.91013965278</v>
@@ -9520,16 +9517,16 @@
         <v>46225.005771516204</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I144" s="5">
         <v>46297</v>
@@ -9547,13 +9544,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9563,7 +9560,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B145" s="9">
         <v>46224.89650905093</v>
@@ -9573,7 +9570,7 @@
         <v>46224.984822025464</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>25</v>
@@ -9597,7 +9594,7 @@
         <v>26</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P145" s="10" t="s">
         <v>26</v>
@@ -9610,7 +9607,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B146" s="5">
         <v>46224.89651261574</v>
@@ -9620,16 +9617,16 @@
         <v>46225.00587975694</v>
       </c>
       <c r="E146" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G146" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="F146" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G146" s="6" t="s">
+      <c r="H146" s="6" t="s">
         <v>342</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>343</v>
       </c>
       <c r="I146" s="5">
         <v>46300</v>
@@ -9647,13 +9644,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q146" s="5">
         <v>46304</v>
@@ -9668,12 +9665,12 @@
         <v>0</v>
       </c>
       <c r="U146" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B147" s="9">
         <v>46224.89652059028</v>
@@ -9683,7 +9680,7 @@
         <v>46224.98672077546</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -9710,13 +9707,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q147" s="9">
         <v>46304</v>
@@ -9731,7 +9728,7 @@
         <v>0</v>
       </c>
       <c r="U147" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -2855,7 +2855,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46224.98722679398</v>
+        <v>46248.17133247685</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>90</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46224.98733012732</v>
+        <v>46248.17133398148</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>74</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46224.98742798611</v>
+        <v>46248.171335231484</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>80</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46224.9888250463</v>
+        <v>46253.2044833449</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>161</v>
@@ -4236,8 +4236,8 @@
       <c r="R47" s="9">
         <v>46260</v>
       </c>
-      <c r="S47" s="7" t="s">
-        <v>32</v>
+      <c r="S47" s="12" t="s">
+        <v>88</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46224.98882244213</v>
+        <v>46253.2044840625</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>166</v>
@@ -4299,8 +4299,8 @@
       <c r="R48" s="5">
         <v>46260</v>
       </c>
-      <c r="S48" s="7" t="s">
-        <v>32</v>
+      <c r="S48" s="12" t="s">
+        <v>88</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46224.98881765046</v>
+        <v>46253.204484120375</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>169</v>
@@ -4362,8 +4362,8 @@
       <c r="R49" s="9">
         <v>46260</v>
       </c>
-      <c r="S49" s="7" t="s">
-        <v>32</v>
+      <c r="S49" s="12" t="s">
+        <v>88</v>
       </c>
       <c r="T49" s="10">
         <v>0</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -4381,7 +4381,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46224.98890766204</v>
+        <v>46254.18319003472</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>172</v>
@@ -4425,8 +4425,8 @@
       <c r="R50" s="5">
         <v>46261</v>
       </c>
-      <c r="S50" s="7" t="s">
-        <v>32</v>
+      <c r="S50" s="12" t="s">
+        <v>88</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46224.9889028125</v>
+        <v>46254.18319019676</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>175</v>
@@ -4488,8 +4488,8 @@
       <c r="R51" s="9">
         <v>46261</v>
       </c>
-      <c r="S51" s="7" t="s">
-        <v>32</v>
+      <c r="S51" s="12" t="s">
+        <v>88</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46224.988900625</v>
+        <v>46254.18319001158</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>178</v>
@@ -4551,8 +4551,8 @@
       <c r="R52" s="5">
         <v>46261</v>
       </c>
-      <c r="S52" s="7" t="s">
-        <v>32</v>
+      <c r="S52" s="12" t="s">
+        <v>88</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -415,7 +415,7 @@
     <t xml:space="preserve">Generacion Oc  OT 4376 </t>
   </si>
   <si>
-    <t xml:space="preserve">propuesta fabricación externa </t>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
   </si>
   <si>
     <t xml:space="preserve">Fabricación externa  OT 4376 ,Armado OT 4376 </t>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46237.55371252315</v>
+        <v>46254.647307129635</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>118</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -3377,7 +3377,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46254.647307129635</v>
+        <v>46255.17030541667</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>118</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -3377,7 +3377,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46255.17030541667</v>
+        <v>46255.6286522338</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>118</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46252.19889861111</v>
+        <v>46259.169297430555</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>83</v>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46224.98722206018</v>
+        <v>46259.16929443287</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46252.19889858796</v>
+        <v>46259.16929560185</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>97</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46224.987326828705</v>
+        <v>46259.169298622684</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>102</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46252.19889856481</v>
+        <v>46259.16929978009</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46224.987424872685</v>
+        <v>46259.16930096065</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>110</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46224.98900751157</v>
+        <v>46259.1920437963</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>77</v>
@@ -4661,8 +4661,8 @@
       <c r="R54" s="5">
         <v>46262</v>
       </c>
-      <c r="S54" s="7" t="s">
-        <v>32</v>
+      <c r="S54" s="12" t="s">
+        <v>88</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -322,235 +322,235 @@
     <t>Generación OC corte laser  OT 4376,Fabricacion corte laser OT 4376</t>
   </si>
   <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1216771795211710</t>
+  </si>
+  <si>
+    <t>Generación OC corte laser  OT 4376</t>
+  </si>
+  <si>
+    <t>Corte Laser  OT 4376 ,Fabricacion corte laser OT 4376</t>
+  </si>
+  <si>
+    <t>1216771795211730</t>
+  </si>
+  <si>
+    <t>Fabricacion corte laser OT 4376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte Laser  OT 4376 ,Recepcion corte laser  OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771795213106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte plasma  OT 4376 </t>
+  </si>
+  <si>
+    <t>Generacion OC Corte plasma  OT 4376,Fabricación corte plasma  OT 4376</t>
+  </si>
+  <si>
+    <t>1216771795213118</t>
+  </si>
+  <si>
+    <t>Corte plasma  OT 4376 ,Fabricación corte plasma  OT 4376</t>
+  </si>
+  <si>
+    <t>1216771898464932</t>
+  </si>
+  <si>
+    <t>Fabricación corte plasma  OT 4376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte plasma  OT 4376 ,Corte plasma  OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771898464949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado OT 4376 </t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4376,Generación OC mecanizado OT 4376</t>
+  </si>
+  <si>
+    <t>1216771973727772</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4376 ,Fabricación Mecanizado OT 4376</t>
+  </si>
+  <si>
+    <t>1216771973727789</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado OT 4376 ,Recepcion mecanizado OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771898495186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa  OT 4376 </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion Oc  OT 4376 ,Armado OT 4376 ,Control de calidad  OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771893506639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion Oc  OT 4376 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa  OT 4376 ,Armado OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771893506656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado OT 4376 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa  OT 4376 ,Control de calidad  OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771893528365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad  OT 4376 </t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1216771893528382</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Preliminar OT 4376 ,Plano Definitivos OT 4376 ,Check pruebas FAT OT 4376 ,Check Planos OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771806162083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Preliminar OT 4376 </t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria y diseñoo:,Plano Definitivos OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771806162105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Definitivos OT 4376 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria y diseñoo:,Check Planos OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771806169487</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Propuesta Fabricación externa  OT 4376 ,Propuesta Mecanizado OT 4376 ,Propuesta Corte plasma  OT 4376 ,propuesta Corte laser OT 4376 ,Ingenieria y diseñoo:,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216772079958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check pruebas FAT OT 4376 </t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216771898520249</t>
+  </si>
+  <si>
+    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT OT 4376 ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216771898520261</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4347 Preparación Materiales,Check pruebas FAT OT 4376 ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1216771795295604</t>
+  </si>
+  <si>
+    <t>1216769310026190</t>
+  </si>
+  <si>
+    <t>1216769310026191</t>
+  </si>
+  <si>
+    <t>1216769310026192</t>
+  </si>
+  <si>
+    <t>1216771893582345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser  OT 4376 ,Recepcion corte plasma  OT 4376 ,Control de calidad Corte plasma OT 4376 ,Recepcion mecanizado OT 4376 ,Control de calidad corte LaserOT 4376 ,Control de calidad Mecanizado OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771893582357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser  OT 4376 </t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,Control de calidad corte LaserOT 4376 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1216771795211710</t>
-  </si>
-  <si>
-    <t>Generación OC corte laser  OT 4376</t>
-  </si>
-  <si>
-    <t>Corte Laser  OT 4376 ,Fabricacion corte laser OT 4376</t>
-  </si>
-  <si>
-    <t>1216771795211730</t>
-  </si>
-  <si>
-    <t>Fabricacion corte laser OT 4376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte Laser  OT 4376 ,Recepcion corte laser  OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771795213106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte plasma  OT 4376 </t>
-  </si>
-  <si>
-    <t>Generacion OC Corte plasma  OT 4376,Fabricación corte plasma  OT 4376</t>
-  </si>
-  <si>
-    <t>1216771795213118</t>
-  </si>
-  <si>
-    <t>Corte plasma  OT 4376 ,Fabricación corte plasma  OT 4376</t>
-  </si>
-  <si>
-    <t>1216771898464932</t>
-  </si>
-  <si>
-    <t>Fabricación corte plasma  OT 4376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte plasma  OT 4376 ,Corte plasma  OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771898464949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado OT 4376 </t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4376,Generación OC mecanizado OT 4376</t>
-  </si>
-  <si>
-    <t>1216771973727772</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4376 ,Fabricación Mecanizado OT 4376</t>
-  </si>
-  <si>
-    <t>1216771973727789</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado OT 4376 ,Recepcion mecanizado OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771898495186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa  OT 4376 </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion Oc  OT 4376 ,Armado OT 4376 ,Control de calidad  OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771893506639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion Oc  OT 4376 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa  OT 4376 ,Armado OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771893506656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado OT 4376 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa  OT 4376 ,Control de calidad  OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771893528365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad  OT 4376 </t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1216771893528382</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Preliminar OT 4376 ,Plano Definitivos OT 4376 ,Check pruebas FAT OT 4376 ,Check Planos OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771806162083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Preliminar OT 4376 </t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria y diseñoo:,Plano Definitivos OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771806162105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Definitivos OT 4376 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria y diseñoo:,Check Planos OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771806169487</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Propuesta Fabricación externa  OT 4376 ,Propuesta Mecanizado OT 4376 ,Propuesta Corte plasma  OT 4376 ,propuesta Corte laser OT 4376 ,Ingenieria y diseñoo:,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216772079958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check pruebas FAT OT 4376 </t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216771898520249</t>
-  </si>
-  <si>
-    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT OT 4376 ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216771898520261</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4347 Preparación Materiales,Check pruebas FAT OT 4376 ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1216771795295604</t>
-  </si>
-  <si>
-    <t>1216769310026190</t>
-  </si>
-  <si>
-    <t>1216769310026191</t>
-  </si>
-  <si>
-    <t>1216769310026192</t>
-  </si>
-  <si>
-    <t>1216771893582345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser  OT 4376 ,Recepcion corte plasma  OT 4376 ,Control de calidad Corte plasma OT 4376 ,Recepcion mecanizado OT 4376 ,Control de calidad corte LaserOT 4376 ,Control de calidad Mecanizado OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771893582357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser  OT 4376 </t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,Control de calidad corte LaserOT 4376 </t>
   </si>
   <si>
     <t>1216771893582539</t>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46259.169297430555</v>
+        <v>46260.18545297453</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>83</v>
@@ -2839,19 +2839,19 @@
       <c r="R22" s="5">
         <v>46247</v>
       </c>
-      <c r="S22" s="12" t="s">
-        <v>88</v>
+      <c r="S22" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B23" s="9">
         <v>46224.895839062505</v>
@@ -2861,7 +2861,7 @@
         <v>46248.17133247685</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2894,7 +2894,7 @@
         <v>67</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2905,12 +2905,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5">
         <v>46224.8958440162</v>
@@ -2920,7 +2920,7 @@
         <v>46259.16929443287</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2950,10 +2950,10 @@
         <v>83</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2964,22 +2964,22 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B25" s="9">
         <v>46224.89584935185</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46259.16929560185</v>
+        <v>46260.18545321759</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -3009,7 +3009,7 @@
         <v>82</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3020,19 +3020,19 @@
       <c r="R25" s="9">
         <v>46247</v>
       </c>
-      <c r="S25" s="12" t="s">
-        <v>88</v>
+      <c r="S25" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" s="5">
         <v>46224.895853553244</v>
@@ -3069,13 +3069,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>73</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3085,7 +3085,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="9">
         <v>46224.895863321755</v>
@@ -3095,7 +3095,7 @@
         <v>46259.169298622684</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3122,13 +3122,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>74</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3138,17 +3138,17 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46224.89586804398</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46259.16929978009</v>
+        <v>46260.18545319444</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3178,7 +3178,7 @@
         <v>82</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3189,19 +3189,19 @@
       <c r="R28" s="5">
         <v>46247</v>
       </c>
-      <c r="S28" s="12" t="s">
-        <v>88</v>
+      <c r="S28" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B29" s="9">
         <v>46224.895871886576</v>
@@ -3238,13 +3238,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B30" s="5">
         <v>46224.89587627315</v>
@@ -3264,7 +3264,7 @@
         <v>46259.16930096065</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3291,13 +3291,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>80</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3307,7 +3307,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B31" s="9">
         <v>46224.89588070602</v>
@@ -3317,16 +3317,16 @@
         <v>46224.9875411574</v>
       </c>
       <c r="E31" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
+      <c r="H31" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3347,7 +3347,7 @@
         <v>82</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -3365,12 +3365,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46224.89592390046</v>
@@ -3380,16 +3380,16 @@
         <v>46255.6286522338</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="I32" s="5">
         <v>46247</v>
@@ -3407,13 +3407,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O32" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P32" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B33" s="9">
         <v>46224.89592935186</v>
@@ -3433,16 +3433,16 @@
         <v>46224.987624201385</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="I33" s="9">
         <v>46258</v>
@@ -3460,13 +3460,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3476,7 +3476,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46224.89593387731</v>
@@ -3486,16 +3486,16 @@
         <v>46224.98774165509</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3513,13 +3513,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3529,7 +3529,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B35" s="9">
         <v>46224.89593827546</v>
@@ -3539,7 +3539,7 @@
         <v>46238.486380925926</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3563,7 +3563,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3576,7 +3576,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B36" s="5">
         <v>46224.895942546296</v>
@@ -3588,16 +3588,16 @@
         <v>46235.17742733796</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3615,13 +3615,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3641,7 +3641,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B37" s="9">
         <v>46224.895948425925</v>
@@ -3653,16 +3653,16 @@
         <v>46242.177803032406</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>134</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3680,13 +3680,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46224.895953506944</v>
@@ -3724,10 +3724,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3745,13 +3745,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3771,7 +3771,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B39" s="9">
         <v>46224.89596851852</v>
@@ -3781,16 +3781,16 @@
         <v>46224.9887275463</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="I39" s="9">
         <v>46290</v>
@@ -3808,13 +3808,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3829,12 +3829,12 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46224.89597322917</v>
@@ -3844,16 +3844,16 @@
         <v>46224.98802077546</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3869,13 +3869,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="P40" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="P40" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3885,7 +3885,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B41" s="9">
         <v>46224.89597747685</v>
@@ -3895,16 +3895,16 @@
         <v>46224.988017592594</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3920,13 +3920,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3936,7 +3936,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46224.89600425926</v>
@@ -3946,16 +3946,16 @@
         <v>46224.98801423611</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -3971,13 +3971,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O42" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B43" s="9">
         <v>46224.90846989583</v>
@@ -3997,16 +3997,16 @@
         <v>46224.988011203706</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="9">
@@ -4022,13 +4022,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O43" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="P43" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="P43" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4038,7 +4038,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B44" s="5">
         <v>46224.908482824074</v>
@@ -4048,16 +4048,16 @@
         <v>46224.98800859954</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -4073,13 +4073,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O44" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4089,7 +4089,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B45" s="9">
         <v>46224.908498171295</v>
@@ -4099,16 +4099,16 @@
         <v>46224.98800302083</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="9">
@@ -4124,13 +4124,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O45" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="P45" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="P45" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B46" s="5">
         <v>46224.89600854166</v>
@@ -4150,7 +4150,7 @@
         <v>46224.97705253473</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4174,7 +4174,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4187,26 +4187,26 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B47" s="9">
         <v>46224.896012384255</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46253.2044833449</v>
+        <v>46260.169285578704</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="9">
@@ -4222,13 +4222,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q47" s="9">
         <v>46260</v>
@@ -4237,13 +4237,13 @@
         <v>46260</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46253.2044840625</v>
+        <v>46260.16928753472</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>166</v>
@@ -4264,10 +4264,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I48" s="5">
         <v>46260</v>
@@ -4285,10 +4285,10 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>167</v>
@@ -4300,13 +4300,13 @@
         <v>46260</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46253.204484120375</v>
+        <v>46260.169288634264</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>169</v>
@@ -4327,10 +4327,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I49" s="9">
         <v>46260</v>
@@ -4348,10 +4348,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>170</v>
@@ -4363,13 +4363,13 @@
         <v>46260</v>
       </c>
       <c r="S49" s="12" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="T49" s="10">
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4390,10 +4390,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I50" s="5">
         <v>46261</v>
@@ -4411,10 +4411,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>173</v>
@@ -4426,13 +4426,13 @@
         <v>46261</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4453,10 +4453,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="I51" s="9">
         <v>46261</v>
@@ -4474,7 +4474,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>166</v>
@@ -4489,13 +4489,13 @@
         <v>46261</v>
       </c>
       <c r="S51" s="12" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4516,10 +4516,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I52" s="5">
         <v>46261</v>
@@ -4537,7 +4537,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>169</v>
@@ -4552,13 +4552,13 @@
         <v>46261</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4662,13 +4662,13 @@
         <v>46262</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4683,7 +4683,7 @@
         <v>46224.98900451389</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4713,7 +4713,7 @@
         <v>181</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>181</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4746,7 +4746,7 @@
         <v>46238.48636976852</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4773,7 +4773,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>189</v>
@@ -4799,7 +4799,7 @@
         <v>46238.4863703588</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4826,7 +4826,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>192</v>
@@ -4852,7 +4852,7 @@
         <v>46238.48638123843</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4879,7 +4879,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>195</v>
@@ -4905,7 +4905,7 @@
         <v>46224.992584293985</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -4932,7 +4932,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>77</v>
@@ -4958,7 +4958,7 @@
         <v>46224.99258355324</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4985,7 +4985,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>77</v>
@@ -5011,7 +5011,7 @@
         <v>46224.99258276621</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5038,7 +5038,7 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>77</v>
@@ -5070,10 +5070,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5112,7 +5112,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5127,16 +5127,16 @@
         <v>46238.486370949075</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="I63" s="9">
         <v>46274</v>
@@ -5180,16 +5180,16 @@
         <v>46238.486371377316</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I64" s="5">
         <v>46274</v>
@@ -5233,16 +5233,16 @@
         <v>46238.486371782405</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="I65" s="9">
         <v>46274</v>
@@ -5286,16 +5286,16 @@
         <v>46225.00151444445</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I66" s="5">
         <v>46274</v>
@@ -5316,7 +5316,7 @@
         <v>201</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>205</v>
@@ -5339,16 +5339,16 @@
         <v>46225.00151381944</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="I67" s="9">
         <v>46274</v>
@@ -5369,7 +5369,7 @@
         <v>201</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>205</v>
@@ -5398,10 +5398,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5422,7 +5422,7 @@
         <v>201</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>205</v>
@@ -5498,10 +5498,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I70" s="5">
         <v>46230</v>
@@ -5540,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5561,10 +5561,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I71" s="9">
         <v>46230</v>
@@ -5603,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5624,10 +5624,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I72" s="5">
         <v>46230</v>
@@ -5666,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5758,7 +5758,7 @@
         <v>225</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>225</v>
@@ -5776,7 +5776,7 @@
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5791,7 +5791,7 @@
         <v>46225.00190993056</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5821,7 +5821,7 @@
         <v>228</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>230</v>
@@ -5844,7 +5844,7 @@
         <v>46225.00190693287</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5874,7 +5874,7 @@
         <v>228</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>230</v>
@@ -5897,7 +5897,7 @@
         <v>46225.00190398148</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5927,7 +5927,7 @@
         <v>228</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>233</v>
@@ -5950,7 +5950,7 @@
         <v>46225.00190130787</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5980,7 +5980,7 @@
         <v>228</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>235</v>
@@ -6003,7 +6003,7 @@
         <v>46225.00189846064</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6033,7 +6033,7 @@
         <v>228</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>235</v>
@@ -6056,7 +6056,7 @@
         <v>46225.0018940625</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6139,7 +6139,7 @@
         <v>225</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>225</v>
@@ -6157,7 +6157,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6172,7 +6172,7 @@
         <v>46238.48638170139</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6223,7 +6223,7 @@
         <v>46238.486382233794</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6274,7 +6274,7 @@
         <v>46238.486382800926</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6325,7 +6325,7 @@
         <v>46225.00341435186</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6353,7 +6353,7 @@
         <v>239</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>245</v>
@@ -6376,7 +6376,7 @@
         <v>46225.003411944446</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6404,7 +6404,7 @@
         <v>239</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>245</v>
@@ -6427,7 +6427,7 @@
         <v>46225.003407199074</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6455,7 +6455,7 @@
         <v>239</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>245</v>
@@ -6508,7 +6508,7 @@
         <v>225</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>225</v>
@@ -6526,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6541,7 +6541,7 @@
         <v>46225.00360141204</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6594,7 +6594,7 @@
         <v>46225.003598587966</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6647,7 +6647,7 @@
         <v>46225.00359555555</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6700,7 +6700,7 @@
         <v>46225.003592696754</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6730,7 +6730,7 @@
         <v>250</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>253</v>
@@ -6753,7 +6753,7 @@
         <v>46225.00358984954</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6783,7 +6783,7 @@
         <v>250</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>253</v>
@@ -6806,7 +6806,7 @@
         <v>46225.003585150465</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6836,7 +6836,7 @@
         <v>250</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>260</v>
@@ -6907,7 +6907,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -6922,7 +6922,7 @@
         <v>46238.48637237269</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6975,7 +6975,7 @@
         <v>46238.486383379626</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7028,7 +7028,7 @@
         <v>46225.003931203704</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7081,7 +7081,7 @@
         <v>46225.003927453705</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7111,7 +7111,7 @@
         <v>262</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>269</v>
@@ -7134,7 +7134,7 @@
         <v>46225.0039243287</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7164,7 +7164,7 @@
         <v>262</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>269</v>
@@ -7217,7 +7217,7 @@
         <v>262</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>269</v>
@@ -7270,7 +7270,7 @@
         <v>225</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>225</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="U102" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
@@ -7303,7 +7303,7 @@
         <v>46225.004084687505</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7356,7 +7356,7 @@
         <v>46225.00408194444</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7409,7 +7409,7 @@
         <v>46225.00407914352</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7462,7 +7462,7 @@
         <v>46225.00407667824</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7492,7 +7492,7 @@
         <v>274</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>281</v>
@@ -7515,7 +7515,7 @@
         <v>46225.00407431713</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7545,7 +7545,7 @@
         <v>274</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>281</v>
@@ -7568,7 +7568,7 @@
         <v>46225.00406917824</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7651,7 +7651,7 @@
         <v>225</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>225</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -7684,7 +7684,7 @@
         <v>46225.00432578704</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7714,7 +7714,7 @@
         <v>285</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>287</v>
@@ -7737,7 +7737,7 @@
         <v>46225.00432245371</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7767,7 +7767,7 @@
         <v>285</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>287</v>
@@ -7790,7 +7790,7 @@
         <v>46225.00431880787</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7820,7 +7820,7 @@
         <v>285</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>287</v>
@@ -7843,7 +7843,7 @@
         <v>46225.00431532407</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -7873,7 +7873,7 @@
         <v>285</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>287</v>
@@ -7896,7 +7896,7 @@
         <v>46225.00431230324</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7926,7 +7926,7 @@
         <v>285</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>287</v>
@@ -7949,7 +7949,7 @@
         <v>46225.00430677083</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -7979,7 +7979,7 @@
         <v>285</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>287</v>
@@ -8079,7 +8079,7 @@
         <v>294</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>300</v>
@@ -8097,7 +8097,7 @@
         <v>0</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -8112,7 +8112,7 @@
         <v>46225.00456991898</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8142,7 +8142,7 @@
         <v>297</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>302</v>
@@ -8165,7 +8165,7 @@
         <v>46225.004566655094</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8195,7 +8195,7 @@
         <v>297</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>302</v>
@@ -8218,7 +8218,7 @@
         <v>46225.00456336806</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8248,7 +8248,7 @@
         <v>297</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>302</v>
@@ -8271,7 +8271,7 @@
         <v>46225.00456075231</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8301,7 +8301,7 @@
         <v>297</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>302</v>
@@ -8324,7 +8324,7 @@
         <v>46225.00455841435</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8354,7 +8354,7 @@
         <v>297</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>302</v>
@@ -8377,7 +8377,7 @@
         <v>46225.00455403935</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8407,7 +8407,7 @@
         <v>297</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>302</v>
@@ -8478,7 +8478,7 @@
         <v>0</v>
       </c>
       <c r="U124" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
@@ -8493,7 +8493,7 @@
         <v>46225.00484849537</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8523,7 +8523,7 @@
         <v>309</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>312</v>
@@ -8546,7 +8546,7 @@
         <v>46225.00484502315</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8576,7 +8576,7 @@
         <v>309</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>312</v>
@@ -8599,7 +8599,7 @@
         <v>46225.0048419213</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -8629,7 +8629,7 @@
         <v>309</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>312</v>
@@ -8652,7 +8652,7 @@
         <v>46225.00483878472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8682,7 +8682,7 @@
         <v>309</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>312</v>
@@ -8705,7 +8705,7 @@
         <v>46225.00483302084</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8735,7 +8735,7 @@
         <v>309</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>312</v>
@@ -8758,7 +8758,7 @@
         <v>46225.004831886574</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -8788,7 +8788,7 @@
         <v>309</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>312</v>
@@ -8841,7 +8841,7 @@
         <v>294</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>294</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="U131" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
@@ -8874,7 +8874,7 @@
         <v>46225.00519546296</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -8904,7 +8904,7 @@
         <v>319</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>321</v>
@@ -8927,7 +8927,7 @@
         <v>46225.00519261574</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -8957,7 +8957,7 @@
         <v>319</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P133" s="10" t="s">
         <v>321</v>
@@ -8980,7 +8980,7 @@
         <v>46225.00518949074</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9010,7 +9010,7 @@
         <v>319</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>321</v>
@@ -9033,7 +9033,7 @@
         <v>46225.00518663194</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9063,7 +9063,7 @@
         <v>319</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>321</v>
@@ -9086,7 +9086,7 @@
         <v>46225.0051837963</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9116,7 +9116,7 @@
         <v>319</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>321</v>
@@ -9139,7 +9139,7 @@
         <v>46225.00517873843</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9169,7 +9169,7 @@
         <v>319</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P137" s="10" t="s">
         <v>321</v>
@@ -9222,7 +9222,7 @@
         <v>294</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>329</v>
@@ -9240,7 +9240,7 @@
         <v>0</v>
       </c>
       <c r="U138" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
@@ -9255,7 +9255,7 @@
         <v>46225.00578898148</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9285,7 +9285,7 @@
         <v>328</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>331</v>
@@ -9308,7 +9308,7 @@
         <v>46225.00578587963</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9338,7 +9338,7 @@
         <v>328</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>331</v>
@@ -9361,7 +9361,7 @@
         <v>46225.005782395834</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9391,7 +9391,7 @@
         <v>328</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>331</v>
@@ -9414,7 +9414,7 @@
         <v>46225.00577939815</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9444,7 +9444,7 @@
         <v>328</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>328</v>
@@ -9467,7 +9467,7 @@
         <v>46225.00577614583</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9497,7 +9497,7 @@
         <v>328</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P143" s="10" t="s">
         <v>328</v>
@@ -9520,7 +9520,7 @@
         <v>46225.005771516204</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9550,7 +9550,7 @@
         <v>328</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>328</v>
@@ -9668,7 +9668,7 @@
         <v>0</v>
       </c>
       <c r="U146" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
@@ -9731,7 +9731,7 @@
         <v>0</v>
       </c>
       <c r="U147" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -550,34 +550,34 @@
     <t xml:space="preserve">Bodega ,Control de calidad corte LaserOT 4376 </t>
   </si>
   <si>
+    <t>1216771893582539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte plasma  OT 4376 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,Control de calidad Corte plasma OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771893582561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion mecanizado OT 4376 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,Control de calidad Mecanizado OT 4376 </t>
+  </si>
+  <si>
+    <t>1216772079971096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte LaserOT 4376 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216771893582539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte plasma  OT 4376 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,Control de calidad Corte plasma OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771893582561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion mecanizado OT 4376 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,Control de calidad Mecanizado OT 4376 </t>
-  </si>
-  <si>
-    <t>1216772079971096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte LaserOT 4376 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega </t>
   </si>
   <si>
     <t>1216771893584024</t>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46224.97705253473</v>
+        <v>46261.50044483796</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>157</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46260.169285578704</v>
+        <v>46261.18572775463</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>160</v>
@@ -4236,8 +4236,8 @@
       <c r="R47" s="9">
         <v>46260</v>
       </c>
-      <c r="S47" s="12" t="s">
-        <v>164</v>
+      <c r="S47" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
@@ -4248,17 +4248,17 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B48" s="5">
         <v>46224.896018368054</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46260.16928753472</v>
+        <v>46261.18572780093</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4291,7 +4291,7 @@
         <v>101</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q48" s="5">
         <v>46260</v>
@@ -4299,8 +4299,8 @@
       <c r="R48" s="5">
         <v>46260</v>
       </c>
-      <c r="S48" s="12" t="s">
-        <v>164</v>
+      <c r="S48" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4311,17 +4311,17 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B49" s="9">
         <v>46224.89602424769</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46260.169288634264</v>
+        <v>46261.1857278588</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -4354,7 +4354,7 @@
         <v>109</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q49" s="9">
         <v>46260</v>
@@ -4362,8 +4362,8 @@
       <c r="R49" s="9">
         <v>46260</v>
       </c>
-      <c r="S49" s="12" t="s">
-        <v>164</v>
+      <c r="S49" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T49" s="10">
         <v>0</v>
@@ -4374,17 +4374,17 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B50" s="5">
         <v>46224.89603097222</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46254.18319003472</v>
+        <v>46261.16872184028</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4417,7 +4417,7 @@
         <v>160</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q50" s="5">
         <v>46261</v>
@@ -4426,7 +4426,7 @@
         <v>46261</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4442,9 +4442,11 @@
       <c r="B51" s="9">
         <v>46224.89603738426</v>
       </c>
-      <c r="C51" s="10"/>
+      <c r="C51" s="9">
+        <v>46261.50044034723</v>
+      </c>
       <c r="D51" s="9">
-        <v>46254.18319019676</v>
+        <v>46261.50045407408</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>175</v>
@@ -4477,7 +4479,7 @@
         <v>157</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>176</v>
@@ -4489,13 +4491,13 @@
         <v>46261</v>
       </c>
       <c r="S51" s="12" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="T51" s="10">
-        <v>0</v>
-      </c>
-      <c r="U51" s="11" t="s">
-        <v>88</v>
+        <v>1</v>
+      </c>
+      <c r="U51" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4507,7 +4509,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46254.18319001158</v>
+        <v>46261.16872083333</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>178</v>
@@ -4540,7 +4542,7 @@
         <v>157</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>179</v>
@@ -4552,7 +4554,7 @@
         <v>46261</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4662,7 +4664,7 @@
         <v>46262</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4743,7 +4745,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46238.48636976852</v>
+        <v>46261.50044427083</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>148</v>
@@ -4796,7 +4798,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46238.4863703588</v>
+        <v>46261.50044546297</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>148</v>
@@ -4849,7 +4851,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46238.48638123843</v>
+        <v>46261.50044616898</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>148</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -577,46 +577,46 @@
     <t xml:space="preserve">OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega </t>
   </si>
   <si>
+    <t>1216771893584024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma OT 4376 </t>
+  </si>
+  <si>
+    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216771893584046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado OT 4376 </t>
+  </si>
+  <si>
+    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216772079988850</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparacion materiales OT 4376 ,Armado OT 4376 ,Control de calidad Armado OT 4376 </t>
+  </si>
+  <si>
+    <t>1216772079988862</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Caldereria,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216771893584024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma OT 4376 </t>
-  </si>
-  <si>
-    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216771893584046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado OT 4376 </t>
-  </si>
-  <si>
-    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216772079988850</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparacion materiales OT 4376 ,Armado OT 4376 ,Control de calidad Armado OT 4376 </t>
-  </si>
-  <si>
-    <t>1216772079988862</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Caldereria,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1216771795315070</t>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46261.16872184028</v>
+        <v>46262.19370900463</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>171</v>
@@ -4425,8 +4425,8 @@
       <c r="R50" s="5">
         <v>46261</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>173</v>
+      <c r="S50" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4437,7 +4437,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B51" s="9">
         <v>46224.89603738426</v>
@@ -4446,10 +4446,10 @@
         <v>46261.50044034723</v>
       </c>
       <c r="D51" s="9">
-        <v>46261.50045407408</v>
+        <v>46262.19370895834</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4482,7 +4482,7 @@
         <v>165</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q51" s="9">
         <v>46261</v>
@@ -4490,8 +4490,8 @@
       <c r="R51" s="9">
         <v>46261</v>
       </c>
-      <c r="S51" s="12" t="s">
-        <v>173</v>
+      <c r="S51" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T51" s="10">
         <v>1</v>
@@ -4502,17 +4502,17 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B52" s="5">
         <v>46224.89604363426</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46261.16872083333</v>
+        <v>46262.193708923616</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4545,7 +4545,7 @@
         <v>168</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q52" s="5">
         <v>46261</v>
@@ -4553,8 +4553,8 @@
       <c r="R52" s="5">
         <v>46261</v>
       </c>
-      <c r="S52" s="12" t="s">
-        <v>173</v>
+      <c r="S52" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B53" s="9">
         <v>46224.89604989583</v>
@@ -4575,7 +4575,7 @@
         <v>46224.978400416665</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4599,7 +4599,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4612,7 +4612,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B54" s="5">
         <v>46224.8960534375</v>
@@ -4628,10 +4628,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46262</v>
@@ -4649,13 +4649,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q54" s="5">
         <v>46266</v>
@@ -4664,7 +4664,7 @@
         <v>46262</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4691,10 +4691,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I55" s="9">
         <v>46267</v>
@@ -4712,13 +4712,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q55" s="9">
         <v>46273</v>
@@ -4754,10 +4754,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I56" s="5">
         <v>46267</v>
@@ -4807,10 +4807,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I57" s="9">
         <v>46267</v>
@@ -4860,10 +4860,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I58" s="5">
         <v>46267</v>
@@ -4913,10 +4913,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I59" s="9">
         <v>46267</v>
@@ -4966,10 +4966,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I60" s="5">
         <v>46267</v>
@@ -5019,10 +5019,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I61" s="9">
         <v>46267</v>
@@ -5093,13 +5093,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>202</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q62" s="5">
         <v>46274</v>
@@ -8819,10 +8819,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I131" s="9">
         <v>46296</v>
@@ -8882,10 +8882,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I132" s="5">
         <v>46296</v>
@@ -8935,10 +8935,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I133" s="9">
         <v>46296</v>
@@ -8988,10 +8988,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I134" s="5">
         <v>46296</v>
@@ -9041,10 +9041,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H135" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I135" s="9">
         <v>46296</v>
@@ -9094,10 +9094,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I136" s="5">
         <v>46296</v>
@@ -9147,10 +9147,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H137" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H137" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I137" s="9">
         <v>46296</v>
@@ -9200,10 +9200,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I138" s="5">
         <v>46297</v>
@@ -9263,10 +9263,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H139" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H139" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I139" s="9">
         <v>46297</v>
@@ -9316,10 +9316,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I140" s="5">
         <v>46297</v>
@@ -9369,10 +9369,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H141" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H141" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I141" s="9">
         <v>46297</v>
@@ -9422,10 +9422,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I142" s="5">
         <v>46297</v>
@@ -9475,10 +9475,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H143" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I143" s="9">
         <v>46297</v>
@@ -9528,10 +9528,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I144" s="5">
         <v>46297</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -4619,7 +4619,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46259.1920437963</v>
+        <v>46266.16958828704</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>77</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46224.98900451389</v>
+        <v>46266.1974974537</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>121</v>
@@ -4726,8 +4726,8 @@
       <c r="R55" s="9">
         <v>46267</v>
       </c>
-      <c r="S55" s="7" t="s">
-        <v>32</v>
+      <c r="S55" s="12" t="s">
+        <v>186</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -616,10 +616,10 @@
     <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Caldereria,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
+    <t>1216771795315070</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216771795315070</t>
   </si>
   <si>
     <t>1216771795323400</t>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46266.16958828704</v>
+        <v>46267.190341608795</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>77</v>
@@ -4663,8 +4663,8 @@
       <c r="R54" s="5">
         <v>46262</v>
       </c>
-      <c r="S54" s="12" t="s">
-        <v>186</v>
+      <c r="S54" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4675,7 +4675,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B55" s="9">
         <v>46224.89605969907</v>
@@ -4727,7 +4727,7 @@
         <v>46267</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46225.00135394676</v>
+        <v>46267.18607484954</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>201</v>
@@ -5107,8 +5107,8 @@
       <c r="R62" s="5">
         <v>46274</v>
       </c>
-      <c r="S62" s="7" t="s">
-        <v>32</v>
+      <c r="S62" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -4682,7 +4682,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46266.1974974537</v>
+        <v>46273.16868394676</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>121</v>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46261.50044427083</v>
+        <v>46273.16868585648</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>148</v>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46261.50044546297</v>
+        <v>46273.16868825231</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>148</v>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46261.50044616898</v>
+        <v>46273.168687094905</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>148</v>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46224.992584293985</v>
+        <v>46273.168658738425</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>148</v>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46224.99258355324</v>
+        <v>46273.16866001158</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>148</v>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46224.99258276621</v>
+        <v>46273.16866116898</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>148</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -619,52 +619,52 @@
     <t>1216771795315070</t>
   </si>
   <si>
+    <t>1216771795323400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado OT 4376 ,Control de calidad corte LaserOT 4376 ,Control de calidad Corte plasma OT 4376 ,Check Planos OT 4376 ,Preparacion materiales OT 4376 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Armado OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771973834397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Planos OT 4376 ,Preparacion materiales OT 4376 ,Control de calidad Mecanizado OT 4376 ,Control de calidad corte LaserOT 4376 ,Control de calidad Corte plasma OT 4376 </t>
+  </si>
+  <si>
+    <t>Armado OT 4376 ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216771898460356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparacion materiales OT 4376 ,Control de calidad corte LaserOT 4376 ,Control de calidad Corte plasma OT 4376 ,Control de calidad Mecanizado OT 4376 ,Check Planos OT 4376 </t>
+  </si>
+  <si>
+    <t>1216769310026193</t>
+  </si>
+  <si>
+    <t>1216769310026194</t>
+  </si>
+  <si>
+    <t>1216769310026195</t>
+  </si>
+  <si>
+    <t>Armado OT 4376 ,OT  4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216772080031292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Armado OT 4376 </t>
+  </si>
+  <si>
+    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT  4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216771795323400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado OT 4376 ,Control de calidad corte LaserOT 4376 ,Control de calidad Corte plasma OT 4376 ,Check Planos OT 4376 ,Preparacion materiales OT 4376 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Armado OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771973834397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Planos OT 4376 ,Preparacion materiales OT 4376 ,Control de calidad Mecanizado OT 4376 ,Control de calidad corte LaserOT 4376 ,Control de calidad Corte plasma OT 4376 </t>
-  </si>
-  <si>
-    <t>Armado OT 4376 ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216771898460356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparacion materiales OT 4376 ,Control de calidad corte LaserOT 4376 ,Control de calidad Corte plasma OT 4376 ,Control de calidad Mecanizado OT 4376 ,Check Planos OT 4376 </t>
-  </si>
-  <si>
-    <t>1216769310026193</t>
-  </si>
-  <si>
-    <t>1216769310026194</t>
-  </si>
-  <si>
-    <t>1216769310026195</t>
-  </si>
-  <si>
-    <t>Armado OT 4376 ,OT  4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216772080031292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Armado OT 4376 </t>
-  </si>
-  <si>
-    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT  4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1216771795359890</t>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46273.16868394676</v>
+        <v>46274.16186678241</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>121</v>
@@ -4726,8 +4726,8 @@
       <c r="R55" s="9">
         <v>46267</v>
       </c>
-      <c r="S55" s="12" t="s">
-        <v>187</v>
+      <c r="S55" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B56" s="5">
         <v>46224.89606466435</v>
@@ -4778,10 +4778,10 @@
         <v>121</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B57" s="9">
         <v>46224.89607361111</v>
@@ -4831,10 +4831,10 @@
         <v>121</v>
       </c>
       <c r="O57" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P57" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4844,7 +4844,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B58" s="5">
         <v>46224.89613331019</v>
@@ -4884,10 +4884,10 @@
         <v>121</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4897,7 +4897,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B59" s="9">
         <v>46224.90866162037</v>
@@ -4940,7 +4940,7 @@
         <v>77</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4950,7 +4950,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B60" s="5">
         <v>46224.90867304398</v>
@@ -4993,7 +4993,7 @@
         <v>77</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5003,7 +5003,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B61" s="9">
         <v>46224.90868626157</v>
@@ -5046,7 +5046,7 @@
         <v>77</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5056,17 +5056,17 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B62" s="5">
         <v>46224.89614391203</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46267.18607484954</v>
+        <v>46274.16860659722</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5096,7 +5096,7 @@
         <v>180</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>180</v>
@@ -5108,7 +5108,7 @@
         <v>46274</v>
       </c>
       <c r="S62" s="12" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46238.486370949075</v>
+        <v>46274.16860311343</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>148</v>
@@ -5156,7 +5156,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>204</v>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46238.486371377316</v>
+        <v>46274.16860428241</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>148</v>
@@ -5209,7 +5209,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>204</v>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46238.486371782405</v>
+        <v>46274.16860553241</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>148</v>
@@ -5262,7 +5262,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>204</v>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46225.00151444445</v>
+        <v>46274.168593078706</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>148</v>
@@ -5315,7 +5315,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>148</v>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46225.00151381944</v>
+        <v>46274.16859423611</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>148</v>
@@ -5368,7 +5368,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>148</v>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46225.001513020834</v>
+        <v>46274.16859528935</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>211</v>
@@ -5421,7 +5421,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>148</v>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46225.00179069444</v>
+        <v>46274.15436547453</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>228</v>
@@ -5771,8 +5771,8 @@
       <c r="R74" s="5">
         <v>46275</v>
       </c>
-      <c r="S74" s="7" t="s">
-        <v>32</v>
+      <c r="S74" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
@@ -6891,7 +6891,7 @@
         <v>225</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>225</v>

--- a/data/50001577-  XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001577-  XEMORTIZ LA CANTERA.xlsx
@@ -664,85 +664,85 @@
     <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT  4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
+    <t>1216771795359890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Check Planos OT 4376 </t>
+  </si>
+  <si>
+    <t>Control de calidad Armado OT 4376 ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216771795360104</t>
+  </si>
+  <si>
+    <t>1216771795360126</t>
+  </si>
+  <si>
+    <t>1216769310026196</t>
+  </si>
+  <si>
+    <t>1216769310026197</t>
+  </si>
+  <si>
+    <t>1216769310026198</t>
+  </si>
+  <si>
+    <t>OT  4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216771795362372</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Alabe OT 4376 ,Recepcion Rodete OT 4376 ,Recepcion motor OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771795362384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Alabe OT 4376 </t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216771973853892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Rodete OT 4376 </t>
+  </si>
+  <si>
+    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega:,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216771973870615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion motor OT 4376 </t>
+  </si>
+  <si>
+    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega:,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216771973870637</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento OT 4376 ,Montaje Alabe OT 4376 ,Montaje Rodete OT 4376 ,RE-PINTADO OT 4376 ,Montaje motor OT 4376 ,Pruebas FAT OT 4376 </t>
+  </si>
+  <si>
+    <t>1216771795377416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento OT 4376 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216771795359890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Check Planos OT 4376 </t>
-  </si>
-  <si>
-    <t>Control de calidad Armado OT 4376 ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216771795360104</t>
-  </si>
-  <si>
-    <t>1216771795360126</t>
-  </si>
-  <si>
-    <t>1216769310026196</t>
-  </si>
-  <si>
-    <t>1216769310026197</t>
-  </si>
-  <si>
-    <t>1216769310026198</t>
-  </si>
-  <si>
-    <t>OT  4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216771795362372</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Alabe OT 4376 ,Recepcion Rodete OT 4376 ,Recepcion motor OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771795362384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Alabe OT 4376 </t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216771973853892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Rodete OT 4376 </t>
-  </si>
-  <si>
-    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega:,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216771973870615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion motor OT 4376 </t>
-  </si>
-  <si>
-    <t>OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega:,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216771973870637</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento OT 4376 ,Montaje Alabe OT 4376 ,Montaje Rodete OT 4376 ,RE-PINTADO OT 4376 ,Montaje motor OT 4376 ,Pruebas FAT OT 4376 </t>
-  </si>
-  <si>
-    <t>1216771795377416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento OT 4376 </t>
   </si>
   <si>
     <t>1216771795377433</t>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46274.16860659722</v>
+        <v>46275.15322010417</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>200</v>
@@ -5107,8 +5107,8 @@
       <c r="R62" s="5">
         <v>46274</v>
       </c>
-      <c r="S62" s="12" t="s">
-        <v>202</v>
+      <c r="S62" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
@@ -5119,7 +5119,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B63" s="9">
         <v>46224.896148935186</v>
@@ -5159,10 +5159,10 @@
         <v>200</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>204</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>205</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5172,7 +5172,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B64" s="5">
         <v>46224.89615454861</v>
@@ -5212,10 +5212,10 @@
         <v>200</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5225,7 +5225,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B65" s="9">
         <v>46224.89616001157</v>
@@ -5265,10 +5265,10 @@
         <v>200</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>204</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>205</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B66" s="5">
         <v>46224.90877734954</v>
@@ -5321,7 +5321,7 @@
         <v>148</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B67" s="9">
         <v>46224.90879113426</v>
@@ -5374,7 +5374,7 @@
         <v>148</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B68" s="5">
         <v>46224.90880622686</v>
@@ -5394,7 +5394,7 @@
         <v>46274.16859528935</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5427,7 +5427,7 @@
         <v>148</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5437,7 +5437,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B69" s="9">
         <v>46224.89616483796</v>
@@ -5447,7 +5447,7 @@
         <v>46224.97892864583</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>25</v>
@@ -5471,7 +5471,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>26</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B70" s="5">
         <v>46224.89616836805</v>
@@ -5494,7 +5494,7 @@
         <v>46232.190274444445</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5521,13 +5521,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>54</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q70" s="5">
         <v>46231</v>
@@ -5547,7 +5547,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B71" s="9">
         <v>46224.89617388889</v>
@@ -5557,7 +5557,7 @@
         <v>46232.19027465278</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5584,13 +5584,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q71" s="9">
         <v>46231</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B72" s="5">
         <v>46224.89617931713</v>
@@ -5620,7 +5620,7 @@
         <v>46232.19027490741</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5647,13 +5647,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -5673,7 +5673,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B73" s="9">
         <v>46224.896184826386</v>
@@ -5683,7 +5683,7 @@
         <v>46224.981535706014</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>25</v>
@@ -5707,7 +5707,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5720,7 +5720,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B74" s="5">
         <v>46224.89618846065</v>
@@ -5730,7 +5730,7 @@
         <v>46274.15436547453</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5757,13 +5757,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q74" s="5">
         <v>46281</v>
@@ -5772,7 +5772,7 @@
         <v>46275</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
@@ -5820,7 +5820,7 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O75" s="10" t="s">
         <v>148</v>
@@ -5873,7 +5873,7 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>148</v>
@@ -5926,7 +5926,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>148</v>
@@ -5979,7 +5979,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>148</v>
@@ -6032,7 +6032,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>148</v>
@@ -6085,10 +6085,10 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>235</v>
@@ -6138,13 +6138,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q81" s="9">
         <v>46286</v>
@@ -6507,13 +6507,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q88" s="5">
         <v>46287</v>
@@ -6888,13 +6888,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>201</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q95" s="9">
         <v>46288</v>
@@ -7189,7 +7189,7 @@
         <v>46225.003918993054</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7269,13 +7269,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q102" s="5">
         <v>46289</v>
@@ -7600,7 +7600,7 @@
         <v>274</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>281</v>
@@ -7650,13 +7650,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>146</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q109" s="9">
         <v>46293</v>
